--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.965</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9116</v>
+        <v>0.8713</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9677</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9128000000000001</v>
+        <v>0.9228000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9778</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9829000000000001</v>
+        <v>0.9792000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9981</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3438000000000001</v>
+        <v>0.4317</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9772</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7988</v>
+        <v>0.8036</v>
       </c>
     </row>
     <row r="9">
@@ -740,7 +740,7 @@
         <v>0.7383</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8896999999999999</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="11">
@@ -820,7 +820,7 @@
         <v>0.9944</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8645</v>
+        <v>0.8326</v>
       </c>
     </row>
     <row r="14">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa de Coleta no Prazo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Taxa de Coleta no Prazo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coleta no Prazo'!$A$1:$H$15</definedName>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1257</v>
+        <v>3028</v>
       </c>
       <c r="D3" t="n">
-        <v>1074</v>
+        <v>2848</v>
       </c>
       <c r="E3" t="n">
-        <v>1213</v>
+        <v>3027</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8543999999999999</v>
+        <v>0.9406</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.965</v>
+        <v>0.9997</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8713</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14798</v>
+        <v>25963</v>
       </c>
       <c r="D4" t="n">
-        <v>10166</v>
+        <v>23841</v>
       </c>
       <c r="E4" t="n">
-        <v>14320</v>
+        <v>24906</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.9183</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9677</v>
+        <v>0.9593</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9228000000000001</v>
+        <v>0.9390999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33737</v>
+        <v>35064</v>
       </c>
       <c r="D6" t="n">
-        <v>25289</v>
+        <v>29183</v>
       </c>
       <c r="E6" t="n">
-        <v>32987</v>
+        <v>33612</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7495999999999999</v>
+        <v>0.8323</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9778</v>
+        <v>0.9586</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9792000000000001</v>
+        <v>0.9904000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4321</v>
+        <v>8023</v>
       </c>
       <c r="D7" t="n">
-        <v>1857</v>
+        <v>6736</v>
       </c>
       <c r="E7" t="n">
-        <v>4313</v>
+        <v>8018</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4298</v>
+        <v>0.8395999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9981</v>
+        <v>0.9994</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4317</v>
+        <v>0.5075</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7234</v>
+        <v>9090</v>
       </c>
       <c r="D8" t="n">
-        <v>4701</v>
+        <v>6344</v>
       </c>
       <c r="E8" t="n">
-        <v>7069</v>
+        <v>9042</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6498</v>
+        <v>0.6979000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9772</v>
+        <v>0.9947</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8036</v>
+        <v>0.9128000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1131</v>
+        <v>1167</v>
       </c>
       <c r="D10" t="n">
-        <v>666</v>
+        <v>835</v>
       </c>
       <c r="E10" t="n">
-        <v>835</v>
+        <v>1030</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.5889</v>
+        <v>0.7155</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.7383</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9125</v>
+        <v>0.9398000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,16 +755,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="3" t="n"/>
+        <v>80</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
@@ -772,7 +776,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -796,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -805,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>536</v>
+        <v>10306</v>
       </c>
       <c r="D13" t="n">
-        <v>495</v>
+        <v>10177</v>
       </c>
       <c r="E13" t="n">
-        <v>533</v>
+        <v>10271</v>
       </c>
       <c r="F13" s="2" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.9965999999999999</v>
+      </c>
+      <c r="H13" s="2" t="n">
         <v>0.9235</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0.9944</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0.8326</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -852,7 +856,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9997</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.872</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9593</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9390999999999999</v>
+        <v>0.9164</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9586</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9904000000000001</v>
+        <v>0.9939</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9994</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5075</v>
+        <v>0.5276</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9947</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9128000000000001</v>
+        <v>0.9029</v>
       </c>
     </row>
     <row r="9">
@@ -740,7 +740,7 @@
         <v>0.8826000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9398000000000001</v>
+        <v>0.9451000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -824,7 +824,7 @@
         <v>0.9965999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9235</v>
+        <v>0.9442</v>
       </c>
     </row>
     <row r="14">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3028</v>
+        <v>2209</v>
       </c>
       <c r="D3" t="n">
-        <v>2848</v>
+        <v>2048</v>
       </c>
       <c r="E3" t="n">
-        <v>3027</v>
+        <v>2208</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9406</v>
+        <v>0.9270999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9997</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.852</v>
+        <v>0.9136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25963</v>
+        <v>22424</v>
       </c>
       <c r="D4" t="n">
-        <v>23841</v>
+        <v>20779</v>
       </c>
       <c r="E4" t="n">
-        <v>24906</v>
+        <v>22049</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9183</v>
+        <v>0.9266</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9593</v>
+        <v>0.9833</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9164</v>
+        <v>0.9066</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35064</v>
+        <v>29514</v>
       </c>
       <c r="D6" t="n">
-        <v>29183</v>
+        <v>25894</v>
       </c>
       <c r="E6" t="n">
-        <v>33612</v>
+        <v>27592</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8323</v>
+        <v>0.8773000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9586</v>
+        <v>0.9349</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9939</v>
+        <v>0.9918</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8023</v>
+        <v>7234</v>
       </c>
       <c r="D7" t="n">
-        <v>6736</v>
+        <v>6532</v>
       </c>
       <c r="E7" t="n">
-        <v>8018</v>
+        <v>7233</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8395999999999999</v>
+        <v>0.903</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5276</v>
+        <v>0.6104999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9090</v>
+        <v>8031</v>
       </c>
       <c r="D8" t="n">
-        <v>6344</v>
+        <v>5920</v>
       </c>
       <c r="E8" t="n">
-        <v>9042</v>
+        <v>6449</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6979000000000001</v>
+        <v>0.7371</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9947</v>
+        <v>0.8029999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9029</v>
+        <v>0.8913</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1167</v>
+        <v>1403</v>
       </c>
       <c r="D10" t="n">
-        <v>835</v>
+        <v>1174</v>
       </c>
       <c r="E10" t="n">
-        <v>1030</v>
+        <v>1322</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7155</v>
+        <v>0.8368000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.9423</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9609000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,7 +776,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10306</v>
+        <v>9455</v>
       </c>
       <c r="D13" t="n">
-        <v>10177</v>
+        <v>9325</v>
       </c>
       <c r="E13" t="n">
-        <v>10271</v>
+        <v>9441</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9875</v>
+        <v>0.9863</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9984999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9442</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2209</v>
+        <v>1867</v>
       </c>
       <c r="D3" t="n">
-        <v>2048</v>
+        <v>1823</v>
       </c>
       <c r="E3" t="n">
-        <v>2208</v>
+        <v>1867</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9270999999999999</v>
+        <v>0.9764</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9136</v>
+        <v>0.9579000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22424</v>
+        <v>19588</v>
       </c>
       <c r="D4" t="n">
-        <v>20779</v>
+        <v>17886</v>
       </c>
       <c r="E4" t="n">
-        <v>22049</v>
+        <v>19577</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9266</v>
+        <v>0.9131</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9833</v>
+        <v>0.9994</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9066</v>
+        <v>0.9187000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29514</v>
+        <v>31546</v>
       </c>
       <c r="D6" t="n">
-        <v>25894</v>
+        <v>27843</v>
       </c>
       <c r="E6" t="n">
-        <v>27592</v>
+        <v>31384</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8773000000000001</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9349</v>
+        <v>0.9948999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9918</v>
+        <v>0.9889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7234</v>
+        <v>6482</v>
       </c>
       <c r="D7" t="n">
-        <v>6532</v>
+        <v>6162</v>
       </c>
       <c r="E7" t="n">
-        <v>7233</v>
+        <v>6478</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.903</v>
+        <v>0.9506</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.9994</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6104999999999999</v>
+        <v>0.6609</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8031</v>
+        <v>7601</v>
       </c>
       <c r="D8" t="n">
-        <v>5920</v>
+        <v>6552</v>
       </c>
       <c r="E8" t="n">
-        <v>6449</v>
+        <v>7589</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7371</v>
+        <v>0.862</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8029999999999999</v>
+        <v>0.9984000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8913</v>
+        <v>0.9157</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1403</v>
+        <v>2089</v>
       </c>
       <c r="D10" t="n">
-        <v>1174</v>
+        <v>1418</v>
       </c>
       <c r="E10" t="n">
-        <v>1322</v>
+        <v>1938</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8368000000000001</v>
+        <v>0.6788</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9423</v>
+        <v>0.9277</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9609000000000001</v>
+        <v>0.9523999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,7 +776,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9455</v>
+        <v>6041</v>
       </c>
       <c r="D13" t="n">
-        <v>9325</v>
+        <v>5903</v>
       </c>
       <c r="E13" t="n">
-        <v>9441</v>
+        <v>6034</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9863</v>
+        <v>0.9772</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9375</v>
+        <v>0.9323999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1867</v>
+        <v>2022</v>
       </c>
       <c r="D3" t="n">
-        <v>1823</v>
+        <v>1997</v>
       </c>
       <c r="E3" t="n">
-        <v>1867</v>
+        <v>1997</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9764</v>
+        <v>0.9876</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1</v>
+        <v>0.9876</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9579000000000001</v>
+        <v>0.8989</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19588</v>
+        <v>19285</v>
       </c>
       <c r="D4" t="n">
-        <v>17886</v>
+        <v>17117</v>
       </c>
       <c r="E4" t="n">
-        <v>19577</v>
+        <v>19216</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9131</v>
+        <v>0.8876000000000001</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.9964</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9187000000000001</v>
+        <v>0.8922</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31546</v>
+        <v>31461</v>
       </c>
       <c r="D6" t="n">
-        <v>27843</v>
+        <v>28067</v>
       </c>
       <c r="E6" t="n">
-        <v>31384</v>
+        <v>31337</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8920999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9948999999999999</v>
+        <v>0.9961</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9889</v>
+        <v>0.9838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6482</v>
+        <v>7252</v>
       </c>
       <c r="D7" t="n">
-        <v>6162</v>
+        <v>6795</v>
       </c>
       <c r="E7" t="n">
-        <v>6478</v>
+        <v>7246</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9506</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.9992</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6609</v>
+        <v>0.6207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7601</v>
+        <v>7156</v>
       </c>
       <c r="D8" t="n">
-        <v>6552</v>
+        <v>6444</v>
       </c>
       <c r="E8" t="n">
-        <v>7589</v>
+        <v>7132</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.862</v>
+        <v>0.9005</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9984000000000001</v>
+        <v>0.9965999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9157</v>
+        <v>0.8719</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2089</v>
+        <v>1045</v>
       </c>
       <c r="D10" t="n">
-        <v>1418</v>
+        <v>1036</v>
       </c>
       <c r="E10" t="n">
-        <v>1938</v>
+        <v>1044</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.6788</v>
+        <v>0.9914000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9277</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9523999999999999</v>
+        <v>0.9882</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,7 +776,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6041</v>
+        <v>4294</v>
       </c>
       <c r="D13" t="n">
-        <v>5903</v>
+        <v>4149</v>
       </c>
       <c r="E13" t="n">
-        <v>6034</v>
+        <v>4155</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9772</v>
+        <v>0.9662000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9676</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9323999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -849,14 +849,12 @@
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2022</v>
+        <v>1997</v>
       </c>
       <c r="D3" t="n">
-        <v>1997</v>
+        <v>1819</v>
       </c>
       <c r="E3" t="n">
-        <v>1997</v>
+        <v>1819</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9876</v>
+        <v>0.9109</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9876</v>
+        <v>0.9109</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8989</v>
+        <v>0.9362</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19285</v>
+        <v>14384</v>
       </c>
       <c r="D4" t="n">
-        <v>17117</v>
+        <v>10979</v>
       </c>
       <c r="E4" t="n">
-        <v>19216</v>
+        <v>13433</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8876000000000001</v>
+        <v>0.7633</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9964</v>
+        <v>0.9339</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8922</v>
+        <v>0.8602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31461</v>
+        <v>23337</v>
       </c>
       <c r="D6" t="n">
-        <v>28067</v>
+        <v>17916</v>
       </c>
       <c r="E6" t="n">
-        <v>31337</v>
+        <v>23295</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8920999999999999</v>
+        <v>0.7676999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9961</v>
+        <v>0.9982</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9838</v>
+        <v>0.9725</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7252</v>
+        <v>5154</v>
       </c>
       <c r="D7" t="n">
-        <v>6795</v>
+        <v>3411</v>
       </c>
       <c r="E7" t="n">
-        <v>7246</v>
+        <v>3411</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9992</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6207</v>
+        <v>0.4387</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7156</v>
+        <v>6607</v>
       </c>
       <c r="D8" t="n">
-        <v>6444</v>
+        <v>5292</v>
       </c>
       <c r="E8" t="n">
-        <v>7132</v>
+        <v>6566</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9005</v>
+        <v>0.8009999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9937999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8719</v>
+        <v>0.8118000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1045</v>
+        <v>1629</v>
       </c>
       <c r="D10" t="n">
-        <v>1036</v>
+        <v>436</v>
       </c>
       <c r="E10" t="n">
-        <v>1044</v>
+        <v>441</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9914000000000001</v>
+        <v>0.2676</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.2707</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9882</v>
+        <v>0.9440999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,7 +776,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4294</v>
+        <v>3302</v>
       </c>
       <c r="D13" t="n">
-        <v>4149</v>
+        <v>2683</v>
       </c>
       <c r="E13" t="n">
-        <v>4155</v>
+        <v>2969</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9662000000000001</v>
+        <v>0.8125</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9676</v>
+        <v>0.8992</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.8798</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1997</v>
+        <v>1164</v>
       </c>
       <c r="D3" t="n">
-        <v>1819</v>
+        <v>440</v>
       </c>
       <c r="E3" t="n">
-        <v>1819</v>
+        <v>440</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9109</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9109</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9362</v>
+        <v>0.8434</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14384</v>
+        <v>10556</v>
       </c>
       <c r="D4" t="n">
-        <v>10979</v>
+        <v>1912</v>
       </c>
       <c r="E4" t="n">
-        <v>13433</v>
+        <v>1912</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7633</v>
+        <v>0.1811</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9339</v>
+        <v>0.1811</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8602</v>
+        <v>0.8381999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23337</v>
+        <v>19292</v>
       </c>
       <c r="D6" t="n">
-        <v>17916</v>
+        <v>8212</v>
       </c>
       <c r="E6" t="n">
-        <v>23295</v>
+        <v>8232</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7676999999999999</v>
+        <v>0.4257</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9982</v>
+        <v>0.4267</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9725</v>
+        <v>0.9676</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5154</v>
+        <v>4461</v>
       </c>
       <c r="D7" t="n">
-        <v>3411</v>
+        <v>885</v>
       </c>
       <c r="E7" t="n">
-        <v>3411</v>
+        <v>885</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.1984</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.1984</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4387</v>
+        <v>0.5779</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6607</v>
+        <v>6099</v>
       </c>
       <c r="D8" t="n">
-        <v>5292</v>
+        <v>1832</v>
       </c>
       <c r="E8" t="n">
-        <v>6566</v>
+        <v>1832</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8009999999999999</v>
+        <v>0.3004</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9937999999999999</v>
+        <v>0.3004</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8118000000000001</v>
+        <v>0.6943</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1629</v>
+        <v>691</v>
       </c>
       <c r="D10" t="n">
-        <v>436</v>
+        <v>178</v>
       </c>
       <c r="E10" t="n">
-        <v>441</v>
+        <v>178</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.2676</v>
+        <v>0.2576</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.2707</v>
+        <v>0.2576</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9440999999999999</v>
+        <v>0.9478</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,20 +755,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
@@ -776,7 +772,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +805,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3302</v>
+        <v>1744</v>
       </c>
       <c r="D13" t="n">
-        <v>2683</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
-        <v>2969</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.8125</v>
+        <v>0.0384</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.8992</v>
+        <v>0.0384</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8798</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -854,7 +850,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1164</v>
+        <v>1303</v>
       </c>
       <c r="D3" t="n">
-        <v>440</v>
+        <v>1066</v>
       </c>
       <c r="E3" t="n">
-        <v>440</v>
+        <v>1066</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.8181</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.8181</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8434</v>
+        <v>0.8773000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10556</v>
+        <v>14229</v>
       </c>
       <c r="D4" t="n">
-        <v>1912</v>
+        <v>10378</v>
       </c>
       <c r="E4" t="n">
-        <v>1912</v>
+        <v>12423</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1811</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1811</v>
+        <v>0.8731</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8066</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19292</v>
+        <v>27915</v>
       </c>
       <c r="D6" t="n">
-        <v>8212</v>
+        <v>20661</v>
       </c>
       <c r="E6" t="n">
-        <v>8232</v>
+        <v>27826</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.4257</v>
+        <v>0.7401000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.4267</v>
+        <v>0.9968</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9676</v>
+        <v>0.9765999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4461</v>
+        <v>4214</v>
       </c>
       <c r="D7" t="n">
-        <v>885</v>
+        <v>1874</v>
       </c>
       <c r="E7" t="n">
-        <v>885</v>
+        <v>4209</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1984</v>
+        <v>0.4447</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1984</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5779</v>
+        <v>0.4839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6099</v>
+        <v>7224</v>
       </c>
       <c r="D8" t="n">
-        <v>1832</v>
+        <v>4250</v>
       </c>
       <c r="E8" t="n">
-        <v>1832</v>
+        <v>6236</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.3004</v>
+        <v>0.5882999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.3004</v>
+        <v>0.8632</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6943</v>
+        <v>0.7105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>691</v>
+        <v>1090</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>880</v>
       </c>
       <c r="E10" t="n">
-        <v>178</v>
+        <v>945</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.2576</v>
+        <v>0.8073</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.2576</v>
+        <v>0.867</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9478</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -772,7 +772,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -805,28 +805,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1744</v>
+        <v>1400</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>1256</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>1375</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.8970999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.0384</v>
+        <v>0.9821</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8884000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,12 +845,14 @@
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="H14" s="2" t="n">
+        <v>0.9333</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1303</v>
+        <v>3758</v>
       </c>
       <c r="D3" t="n">
-        <v>1066</v>
+        <v>3323</v>
       </c>
       <c r="E3" t="n">
-        <v>1066</v>
+        <v>3473</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8181</v>
+        <v>0.8842</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.8181</v>
+        <v>0.9242</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8773000000000001</v>
+        <v>0.9527</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14229</v>
+        <v>21633</v>
       </c>
       <c r="D4" t="n">
-        <v>10378</v>
+        <v>19639</v>
       </c>
       <c r="E4" t="n">
-        <v>12423</v>
+        <v>21018</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7293999999999999</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.8731</v>
+        <v>0.9716</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8066</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27915</v>
+        <v>31726</v>
       </c>
       <c r="D6" t="n">
-        <v>20661</v>
+        <v>27588</v>
       </c>
       <c r="E6" t="n">
-        <v>27826</v>
+        <v>31495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7401000000000001</v>
+        <v>0.8695999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9968</v>
+        <v>0.9926999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9765999999999999</v>
+        <v>0.9723000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4214</v>
+        <v>6656</v>
       </c>
       <c r="D7" t="n">
-        <v>1874</v>
+        <v>5980</v>
       </c>
       <c r="E7" t="n">
-        <v>4209</v>
+        <v>6648</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4447</v>
+        <v>0.8984000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.9987999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4839</v>
+        <v>0.6609</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7224</v>
+        <v>9426</v>
       </c>
       <c r="D8" t="n">
-        <v>4250</v>
+        <v>6393</v>
       </c>
       <c r="E8" t="n">
-        <v>6236</v>
+        <v>8563</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5882999999999999</v>
+        <v>0.6781999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8632</v>
+        <v>0.9084</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7105</v>
+        <v>0.7773</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1090</v>
+        <v>2124</v>
       </c>
       <c r="D10" t="n">
-        <v>880</v>
+        <v>1666</v>
       </c>
       <c r="E10" t="n">
-        <v>945</v>
+        <v>2113</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8073</v>
+        <v>0.7844</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.867</v>
+        <v>0.9948</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8944</v>
+        <v>0.9506999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,16 +755,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="3" t="n"/>
+        <v>93</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
@@ -772,7 +776,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -796,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -805,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1400</v>
+        <v>4957</v>
       </c>
       <c r="D13" t="n">
-        <v>1256</v>
+        <v>4856</v>
       </c>
       <c r="E13" t="n">
-        <v>1375</v>
+        <v>4954</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.8970999999999999</v>
+        <v>0.9795999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9821</v>
+        <v>0.9994</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8884000000000001</v>
+        <v>0.8968</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -835,24 +839,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="3" t="n"/>
+        <v>384</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H14" s="2" t="n">
-        <v>0.9333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3758</v>
+        <v>2276</v>
       </c>
       <c r="D3" t="n">
-        <v>3323</v>
+        <v>2245</v>
       </c>
       <c r="E3" t="n">
-        <v>3473</v>
+        <v>2247</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8842</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9242</v>
+        <v>0.9873000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9527</v>
+        <v>0.9309000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21633</v>
+        <v>16487</v>
       </c>
       <c r="D4" t="n">
-        <v>19639</v>
+        <v>15880</v>
       </c>
       <c r="E4" t="n">
-        <v>21018</v>
+        <v>16275</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9716</v>
+        <v>0.9871</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9251999999999999</v>
+        <v>0.9362999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31726</v>
+        <v>29185</v>
       </c>
       <c r="D6" t="n">
-        <v>27588</v>
+        <v>25709</v>
       </c>
       <c r="E6" t="n">
-        <v>31495</v>
+        <v>28937</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8695999999999999</v>
+        <v>0.8809</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9926999999999999</v>
+        <v>0.9915</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6656</v>
+        <v>6579</v>
       </c>
       <c r="D7" t="n">
-        <v>5980</v>
+        <v>6451</v>
       </c>
       <c r="E7" t="n">
-        <v>6648</v>
+        <v>6573</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8984000000000001</v>
+        <v>0.9804999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6609</v>
+        <v>0.6726000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9426</v>
+        <v>7415</v>
       </c>
       <c r="D8" t="n">
-        <v>6393</v>
+        <v>5421</v>
       </c>
       <c r="E8" t="n">
-        <v>8563</v>
+        <v>7385</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6781999999999999</v>
+        <v>0.7311</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9084</v>
+        <v>0.996</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7773</v>
+        <v>0.8453000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2124</v>
+        <v>2344</v>
       </c>
       <c r="D10" t="n">
-        <v>1666</v>
+        <v>1745</v>
       </c>
       <c r="E10" t="n">
-        <v>2113</v>
+        <v>2260</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7844</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9948</v>
+        <v>0.9642000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9506999999999999</v>
+        <v>0.9495999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>314</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>314</v>
       </c>
       <c r="E11" t="n">
-        <v>93</v>
+        <v>314</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>0.9718000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4957</v>
+        <v>3774</v>
       </c>
       <c r="D13" t="n">
-        <v>4856</v>
+        <v>3581</v>
       </c>
       <c r="E13" t="n">
-        <v>4954</v>
+        <v>3762</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9795999999999999</v>
+        <v>0.9489</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.9968</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8968</v>
+        <v>0.8497</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -839,28 +839,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>384</v>
+        <v>4896</v>
       </c>
       <c r="D14" t="n">
-        <v>384</v>
+        <v>322</v>
       </c>
       <c r="E14" t="n">
-        <v>384</v>
+        <v>3399</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0.0658</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1</v>
+        <v>0.6942</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2276</v>
+        <v>2401</v>
       </c>
       <c r="D3" t="n">
-        <v>2245</v>
+        <v>2317</v>
       </c>
       <c r="E3" t="n">
-        <v>2247</v>
+        <v>2400</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.965</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9873000000000001</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9309000000000001</v>
+        <v>0.9490999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16487</v>
+        <v>16590</v>
       </c>
       <c r="D4" t="n">
-        <v>15880</v>
+        <v>16170</v>
       </c>
       <c r="E4" t="n">
-        <v>16275</v>
+        <v>16578</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9747</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9871</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9362999999999999</v>
+        <v>0.9312</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29185</v>
+        <v>28246</v>
       </c>
       <c r="D6" t="n">
-        <v>25709</v>
+        <v>25277</v>
       </c>
       <c r="E6" t="n">
-        <v>28937</v>
+        <v>28211</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8809</v>
+        <v>0.8948999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9915</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9825</v>
+        <v>0.9826</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6579</v>
+        <v>6245</v>
       </c>
       <c r="D7" t="n">
-        <v>6451</v>
+        <v>6127</v>
       </c>
       <c r="E7" t="n">
-        <v>6573</v>
+        <v>6233</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9804999999999999</v>
+        <v>0.9811</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9991</v>
+        <v>0.9981</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6726000000000001</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7415</v>
+        <v>8675</v>
       </c>
       <c r="D8" t="n">
-        <v>5421</v>
+        <v>7909</v>
       </c>
       <c r="E8" t="n">
-        <v>7385</v>
+        <v>8672</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7311</v>
+        <v>0.9117000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.996</v>
+        <v>0.9997</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8809999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2344</v>
+        <v>2827</v>
       </c>
       <c r="D10" t="n">
-        <v>1745</v>
+        <v>1734</v>
       </c>
       <c r="E10" t="n">
-        <v>2260</v>
+        <v>1734</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.6134000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9642000000000001</v>
+        <v>0.6134000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9495999999999999</v>
+        <v>0.9712000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D11" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E11" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9718000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3774</v>
+        <v>2776</v>
       </c>
       <c r="D13" t="n">
-        <v>3581</v>
+        <v>2760</v>
       </c>
       <c r="E13" t="n">
-        <v>3762</v>
+        <v>2774</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9489</v>
+        <v>0.9942</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9968</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8497</v>
+        <v>0.8896999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -839,28 +839,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4896</v>
+        <v>8520</v>
       </c>
       <c r="D14" t="n">
-        <v>322</v>
+        <v>6147</v>
       </c>
       <c r="E14" t="n">
-        <v>3399</v>
+        <v>6880</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.0658</v>
+        <v>0.7215</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6942</v>
+        <v>0.8075</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6944</v>
+        <v>0.8431999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2401</v>
+        <v>2119</v>
       </c>
       <c r="D3" t="n">
-        <v>2317</v>
+        <v>2041</v>
       </c>
       <c r="E3" t="n">
-        <v>2400</v>
+        <v>2081</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.965</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.9821</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9490999999999999</v>
+        <v>0.9198000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16590</v>
+        <v>16333</v>
       </c>
       <c r="D4" t="n">
-        <v>16170</v>
+        <v>15797</v>
       </c>
       <c r="E4" t="n">
-        <v>16578</v>
+        <v>16302</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9747</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9981</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9312</v>
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28246</v>
+        <v>31239</v>
       </c>
       <c r="D6" t="n">
-        <v>25277</v>
+        <v>30239</v>
       </c>
       <c r="E6" t="n">
-        <v>28211</v>
+        <v>31230</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8948999999999999</v>
+        <v>0.968</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9997</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9826</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6245</v>
+        <v>6675</v>
       </c>
       <c r="D7" t="n">
-        <v>6127</v>
+        <v>6628</v>
       </c>
       <c r="E7" t="n">
-        <v>6233</v>
+        <v>6665</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9811</v>
+        <v>0.993</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9981</v>
+        <v>0.9984999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.631</v>
+        <v>0.6776000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8675</v>
+        <v>7344</v>
       </c>
       <c r="D8" t="n">
-        <v>7909</v>
+        <v>6511</v>
       </c>
       <c r="E8" t="n">
-        <v>8672</v>
+        <v>7329</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9117000000000001</v>
+        <v>0.8865999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9997</v>
+        <v>0.998</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8809999999999999</v>
+        <v>0.8134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2827</v>
+        <v>892</v>
       </c>
       <c r="D10" t="n">
-        <v>1734</v>
+        <v>802</v>
       </c>
       <c r="E10" t="n">
-        <v>1734</v>
+        <v>881</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.6134000000000001</v>
+        <v>0.8991</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.6134000000000001</v>
+        <v>0.9876999999999999</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9712000000000001</v>
+        <v>0.9712999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="D11" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="E11" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2776</v>
+        <v>3267</v>
       </c>
       <c r="D13" t="n">
-        <v>2760</v>
+        <v>3180</v>
       </c>
       <c r="E13" t="n">
-        <v>2774</v>
+        <v>3261</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9942</v>
+        <v>0.9734</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9982</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8896999999999999</v>
+        <v>0.8945000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -839,28 +839,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8520</v>
+        <v>11201</v>
       </c>
       <c r="D14" t="n">
-        <v>6147</v>
+        <v>9427</v>
       </c>
       <c r="E14" t="n">
-        <v>6880</v>
+        <v>10894</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.7215</v>
+        <v>0.8416</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.8075</v>
+        <v>0.9726</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.9209000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2119</v>
+        <v>2530</v>
       </c>
       <c r="D3" t="n">
-        <v>2041</v>
+        <v>2298</v>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>2416</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9083</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9821</v>
+        <v>0.9549</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9198000000000001</v>
+        <v>0.9215000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16333</v>
+        <v>18558</v>
       </c>
       <c r="D4" t="n">
-        <v>15797</v>
+        <v>13687</v>
       </c>
       <c r="E4" t="n">
-        <v>16302</v>
+        <v>17173</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.7375</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9981</v>
+        <v>0.9254000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31239</v>
+        <v>30589</v>
       </c>
       <c r="D6" t="n">
-        <v>30239</v>
+        <v>25870</v>
       </c>
       <c r="E6" t="n">
-        <v>31230</v>
+        <v>30328</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.968</v>
+        <v>0.8456999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9997</v>
+        <v>0.9915</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.978</v>
+        <v>0.9739</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6675</v>
+        <v>6220</v>
       </c>
       <c r="D7" t="n">
-        <v>6628</v>
+        <v>4558</v>
       </c>
       <c r="E7" t="n">
-        <v>6665</v>
+        <v>4558</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.993</v>
+        <v>0.7328</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.7328</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6776000000000001</v>
+        <v>0.6286999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7344</v>
+        <v>6545</v>
       </c>
       <c r="D8" t="n">
-        <v>6511</v>
+        <v>4830</v>
       </c>
       <c r="E8" t="n">
-        <v>7329</v>
+        <v>6406</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8865999999999999</v>
+        <v>0.738</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.998</v>
+        <v>0.9788</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8134</v>
+        <v>0.7454999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="D10" t="n">
-        <v>802</v>
+        <v>606</v>
       </c>
       <c r="E10" t="n">
-        <v>881</v>
+        <v>747</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8991</v>
+        <v>0.6704000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9876999999999999</v>
+        <v>0.8262999999999999</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9712999999999999</v>
+        <v>0.9317</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E11" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3267</v>
+        <v>3130</v>
       </c>
       <c r="D13" t="n">
-        <v>3180</v>
+        <v>2857</v>
       </c>
       <c r="E13" t="n">
-        <v>3261</v>
+        <v>3093</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9734</v>
+        <v>0.9128000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9982</v>
+        <v>0.9882</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8945000000000001</v>
+        <v>0.8345999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -839,28 +839,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11201</v>
+        <v>9945</v>
       </c>
       <c r="D14" t="n">
-        <v>9427</v>
+        <v>7302</v>
       </c>
       <c r="E14" t="n">
-        <v>10894</v>
+        <v>9293</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8416</v>
+        <v>0.7342</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9726</v>
+        <v>0.9344</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.8724</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2530</v>
+        <v>2143</v>
       </c>
       <c r="D3" t="n">
-        <v>2298</v>
+        <v>379</v>
       </c>
       <c r="E3" t="n">
-        <v>2416</v>
+        <v>379</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9083</v>
+        <v>0.1769</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9549</v>
+        <v>0.1769</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9215000000000001</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18558</v>
+        <v>13350</v>
       </c>
       <c r="D4" t="n">
-        <v>13687</v>
+        <v>2499</v>
       </c>
       <c r="E4" t="n">
-        <v>17173</v>
+        <v>2499</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7375</v>
+        <v>0.1872</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9254000000000001</v>
+        <v>0.1872</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9156</v>
+        <v>0.8702</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30589</v>
+        <v>20457</v>
       </c>
       <c r="D6" t="n">
-        <v>25870</v>
+        <v>8127</v>
       </c>
       <c r="E6" t="n">
-        <v>30328</v>
+        <v>8127</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8456999999999999</v>
+        <v>0.3973</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9915</v>
+        <v>0.3973</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9739</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6220</v>
+        <v>5928</v>
       </c>
       <c r="D7" t="n">
-        <v>4558</v>
+        <v>604</v>
       </c>
       <c r="E7" t="n">
-        <v>4558</v>
+        <v>604</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7328</v>
+        <v>0.1019</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.7328</v>
+        <v>0.1019</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6286999999999999</v>
+        <v>0.6766</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6545</v>
+        <v>5552</v>
       </c>
       <c r="D8" t="n">
-        <v>4830</v>
+        <v>661</v>
       </c>
       <c r="E8" t="n">
-        <v>6406</v>
+        <v>661</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.738</v>
+        <v>0.1191</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9788</v>
+        <v>0.1191</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7454999999999999</v>
+        <v>0.6232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>904</v>
+        <v>619</v>
       </c>
       <c r="D10" t="n">
-        <v>606</v>
+        <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>747</v>
+        <v>92</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.6704000000000001</v>
+        <v>0.1486</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8262999999999999</v>
+        <v>0.1486</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9317</v>
+        <v>0.9309000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,7 +776,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +809,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3130</v>
+        <v>1318</v>
       </c>
       <c r="D13" t="n">
-        <v>2857</v>
+        <v>206</v>
       </c>
       <c r="E13" t="n">
-        <v>3093</v>
+        <v>206</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9128000000000001</v>
+        <v>0.1563</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9882</v>
+        <v>0.1563</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8345999999999999</v>
+        <v>0.8438</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -839,28 +839,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9945</v>
+        <v>10041</v>
       </c>
       <c r="D14" t="n">
-        <v>7302</v>
+        <v>1673</v>
       </c>
       <c r="E14" t="n">
-        <v>9293</v>
+        <v>1673</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.7342</v>
+        <v>0.1666</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9344</v>
+        <v>0.1666</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8724</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2143</v>
+        <v>1461</v>
       </c>
       <c r="D3" t="n">
-        <v>379</v>
+        <v>1119</v>
       </c>
       <c r="E3" t="n">
-        <v>379</v>
+        <v>1363</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.1769</v>
+        <v>0.7659</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1769</v>
+        <v>0.9329000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.902</v>
+        <v>0.8756999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13350</v>
+        <v>13028</v>
       </c>
       <c r="D4" t="n">
-        <v>2499</v>
+        <v>9979</v>
       </c>
       <c r="E4" t="n">
-        <v>2499</v>
+        <v>13014</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1872</v>
+        <v>0.7659999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1872</v>
+        <v>0.9989</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8702</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20457</v>
+        <v>32856</v>
       </c>
       <c r="D6" t="n">
-        <v>8127</v>
+        <v>23385</v>
       </c>
       <c r="E6" t="n">
-        <v>8127</v>
+        <v>31055</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.3973</v>
+        <v>0.7117</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3973</v>
+        <v>0.9451999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9759</v>
+        <v>0.9721</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5928</v>
+        <v>5805</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>3136</v>
       </c>
       <c r="E7" t="n">
-        <v>604</v>
+        <v>5797</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1019</v>
+        <v>0.5402</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1019</v>
+        <v>0.9986</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6766</v>
+        <v>0.7303000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5552</v>
+        <v>6130</v>
       </c>
       <c r="D8" t="n">
-        <v>661</v>
+        <v>4085</v>
       </c>
       <c r="E8" t="n">
-        <v>661</v>
+        <v>6107</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1191</v>
+        <v>0.6664</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1191</v>
+        <v>0.9962000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6232</v>
+        <v>0.7687999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,22 +701,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="2" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>619</v>
+        <v>896</v>
       </c>
       <c r="D10" t="n">
-        <v>92</v>
+        <v>866</v>
       </c>
       <c r="E10" t="n">
-        <v>92</v>
+        <v>866</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.1486</v>
+        <v>0.9665</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.1486</v>
+        <v>0.9665</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9309000000000001</v>
+        <v>0.9289000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,7 +782,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1318</v>
+        <v>1094</v>
       </c>
       <c r="D13" t="n">
-        <v>206</v>
+        <v>977</v>
       </c>
       <c r="E13" t="n">
-        <v>206</v>
+        <v>1089</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.1563</v>
+        <v>0.8931</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.1563</v>
+        <v>0.9954000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8438</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -839,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10041</v>
+        <v>8192</v>
       </c>
       <c r="D14" t="n">
-        <v>1673</v>
+        <v>5464</v>
       </c>
       <c r="E14" t="n">
-        <v>1673</v>
+        <v>7986</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.1666</v>
+        <v>0.667</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.1666</v>
+        <v>0.9749</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8547</v>
+        <v>0.8919</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1461</v>
+        <v>2893</v>
       </c>
       <c r="D3" t="n">
-        <v>1119</v>
+        <v>2759</v>
       </c>
       <c r="E3" t="n">
-        <v>1363</v>
+        <v>2823</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.7659</v>
+        <v>0.9537</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9329000000000001</v>
+        <v>0.9758</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8756999999999999</v>
+        <v>0.9355</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13028</v>
+        <v>25336</v>
       </c>
       <c r="D4" t="n">
-        <v>9979</v>
+        <v>24617</v>
       </c>
       <c r="E4" t="n">
-        <v>13014</v>
+        <v>25326</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7659999999999999</v>
+        <v>0.9716</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9989</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.861</v>
+        <v>0.9527</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32856</v>
+        <v>31746</v>
       </c>
       <c r="D6" t="n">
-        <v>23385</v>
+        <v>26921</v>
       </c>
       <c r="E6" t="n">
-        <v>31055</v>
+        <v>31677</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7117</v>
+        <v>0.848</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9451999999999999</v>
+        <v>0.9978</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9721</v>
+        <v>0.9545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5805</v>
+        <v>7769</v>
       </c>
       <c r="D7" t="n">
-        <v>3136</v>
+        <v>6613</v>
       </c>
       <c r="E7" t="n">
-        <v>5797</v>
+        <v>7748</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5402</v>
+        <v>0.8512000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9986</v>
+        <v>0.9973000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7303000000000001</v>
+        <v>0.7314000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6130</v>
+        <v>6548</v>
       </c>
       <c r="D8" t="n">
-        <v>4085</v>
+        <v>5627</v>
       </c>
       <c r="E8" t="n">
-        <v>6107</v>
+        <v>6192</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6664</v>
+        <v>0.8593000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9962000000000001</v>
+        <v>0.9456</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7687999999999999</v>
+        <v>0.7421</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>896</v>
+        <v>1235</v>
       </c>
       <c r="D10" t="n">
-        <v>866</v>
+        <v>1120</v>
       </c>
       <c r="E10" t="n">
-        <v>866</v>
+        <v>1131</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9665</v>
+        <v>0.9068999999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9665</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9289000000000001</v>
+        <v>0.9731000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -782,7 +782,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1094</v>
+        <v>5833</v>
       </c>
       <c r="D13" t="n">
-        <v>977</v>
+        <v>5751</v>
       </c>
       <c r="E13" t="n">
-        <v>1089</v>
+        <v>5823</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.8931</v>
+        <v>0.9859</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9954000000000001</v>
+        <v>0.9983</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.851</v>
+        <v>0.9189000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8192</v>
+        <v>13052</v>
       </c>
       <c r="D14" t="n">
-        <v>5464</v>
+        <v>11059</v>
       </c>
       <c r="E14" t="n">
-        <v>7986</v>
+        <v>12996</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.667</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9749</v>
+        <v>0.9956999999999999</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8919</v>
+        <v>0.9009999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2893</v>
+        <v>2403</v>
       </c>
       <c r="D3" t="n">
-        <v>2759</v>
+        <v>2337</v>
       </c>
       <c r="E3" t="n">
-        <v>2823</v>
+        <v>2363</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9537</v>
+        <v>0.9725</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9758</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9355</v>
+        <v>0.9234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25336</v>
+        <v>17256</v>
       </c>
       <c r="D4" t="n">
-        <v>24617</v>
+        <v>16966</v>
       </c>
       <c r="E4" t="n">
-        <v>25326</v>
+        <v>17225</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9716</v>
+        <v>0.9832</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.9982</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9527</v>
+        <v>0.9418000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31746</v>
+        <v>29594</v>
       </c>
       <c r="D6" t="n">
-        <v>26921</v>
+        <v>25742</v>
       </c>
       <c r="E6" t="n">
-        <v>31677</v>
+        <v>29551</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.848</v>
+        <v>0.8698</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9978</v>
+        <v>0.9984999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9545</v>
+        <v>0.9684999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7769</v>
+        <v>7606</v>
       </c>
       <c r="D7" t="n">
-        <v>6613</v>
+        <v>7526</v>
       </c>
       <c r="E7" t="n">
-        <v>7748</v>
+        <v>7588</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8512000000000001</v>
+        <v>0.9895</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9973000000000001</v>
+        <v>0.9976</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7486</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6548</v>
+        <v>6473</v>
       </c>
       <c r="D8" t="n">
-        <v>5627</v>
+        <v>5662</v>
       </c>
       <c r="E8" t="n">
-        <v>6192</v>
+        <v>6463</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8593000000000001</v>
+        <v>0.8747</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9456</v>
+        <v>0.9984999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7421</v>
+        <v>0.8281999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1235</v>
+        <v>1092</v>
       </c>
       <c r="D10" t="n">
-        <v>1120</v>
+        <v>1036</v>
       </c>
       <c r="E10" t="n">
-        <v>1131</v>
+        <v>1038</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9068999999999999</v>
+        <v>0.9487000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9505</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9731000000000001</v>
+        <v>0.9681000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -782,7 +782,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5833</v>
+        <v>6585</v>
       </c>
       <c r="D13" t="n">
-        <v>5751</v>
+        <v>6479</v>
       </c>
       <c r="E13" t="n">
-        <v>5823</v>
+        <v>6584</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9859</v>
+        <v>0.9839</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9983</v>
+        <v>0.9998</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9264</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13052</v>
+        <v>10526</v>
       </c>
       <c r="D14" t="n">
-        <v>11059</v>
+        <v>9602</v>
       </c>
       <c r="E14" t="n">
-        <v>12996</v>
+        <v>10448</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.9122</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9956999999999999</v>
+        <v>0.9926</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9009999999999999</v>
+        <v>0.9115000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -885,7 +885,9 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H15"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2403</v>
+        <v>1884</v>
       </c>
       <c r="D3" t="n">
-        <v>2337</v>
+        <v>1843</v>
       </c>
       <c r="E3" t="n">
-        <v>2363</v>
+        <v>1871</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9725</v>
+        <v>0.9782</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9931</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9234</v>
+        <v>0.9467</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17256</v>
+        <v>17281</v>
       </c>
       <c r="D4" t="n">
-        <v>16966</v>
+        <v>16882</v>
       </c>
       <c r="E4" t="n">
-        <v>17225</v>
+        <v>17257</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9832</v>
+        <v>0.9769</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9982</v>
+        <v>0.9986</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9418000000000001</v>
+        <v>0.9268999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29594</v>
+        <v>31126</v>
       </c>
       <c r="D6" t="n">
-        <v>25742</v>
+        <v>27760</v>
       </c>
       <c r="E6" t="n">
-        <v>29551</v>
+        <v>31108</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8698</v>
+        <v>0.8919</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9994</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9684999999999999</v>
+        <v>0.9773999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7606</v>
+        <v>7086</v>
       </c>
       <c r="D7" t="n">
-        <v>7526</v>
+        <v>6975</v>
       </c>
       <c r="E7" t="n">
-        <v>7588</v>
+        <v>7033</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9895</v>
+        <v>0.9843000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9976</v>
+        <v>0.9925</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7486</v>
+        <v>0.7617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6473</v>
+        <v>6817</v>
       </c>
       <c r="D8" t="n">
-        <v>5662</v>
+        <v>6386</v>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6386</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8747</v>
+        <v>0.9368000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9368000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8281999999999999</v>
+        <v>0.8395</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1092</v>
+        <v>1370</v>
       </c>
       <c r="D10" t="n">
-        <v>1036</v>
+        <v>1313</v>
       </c>
       <c r="E10" t="n">
-        <v>1038</v>
+        <v>1314</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9487000000000001</v>
+        <v>0.9584</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9505</v>
+        <v>0.9591</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9681000000000001</v>
+        <v>0.9803000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -782,7 +782,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6585</v>
+        <v>2394</v>
       </c>
       <c r="D13" t="n">
-        <v>6479</v>
+        <v>2268</v>
       </c>
       <c r="E13" t="n">
-        <v>6584</v>
+        <v>2386</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9839</v>
+        <v>0.9473999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9998</v>
+        <v>0.9967</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9264</v>
+        <v>0.9222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10526</v>
+        <v>10703</v>
       </c>
       <c r="D14" t="n">
-        <v>9602</v>
+        <v>10024</v>
       </c>
       <c r="E14" t="n">
-        <v>10448</v>
+        <v>10611</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9122</v>
+        <v>0.9366</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9926</v>
+        <v>0.9914000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9115000000000001</v>
+        <v>0.9304000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9931</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9467</v>
+        <v>0.9123</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9986</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9433</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9994</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9773999999999999</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9925</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7617</v>
+        <v>0.7181000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9368000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8395</v>
+        <v>0.8729</v>
       </c>
     </row>
     <row r="9">
@@ -715,9 +715,7 @@
       <c r="G9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -746,7 +744,7 @@
         <v>0.9591</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9803000000000001</v>
+        <v>0.9579000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -830,7 +828,7 @@
         <v>0.9967</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9222</v>
+        <v>0.9153</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +858,7 @@
         <v>0.9914000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9304000000000001</v>
+        <v>0.9151</v>
       </c>
     </row>
     <row r="15">
@@ -885,9 +883,7 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H15" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H15"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1884</v>
+        <v>1468</v>
       </c>
       <c r="D3" t="n">
-        <v>1843</v>
+        <v>481</v>
       </c>
       <c r="E3" t="n">
-        <v>1871</v>
+        <v>481</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9782</v>
+        <v>0.3277</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9931</v>
+        <v>0.3277</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9123</v>
+        <v>0.9135</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17281</v>
+        <v>13395</v>
       </c>
       <c r="D4" t="n">
-        <v>16882</v>
+        <v>2280</v>
       </c>
       <c r="E4" t="n">
-        <v>17257</v>
+        <v>2280</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9769</v>
+        <v>0.1702</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9986</v>
+        <v>0.1702</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9433</v>
+        <v>0.8434999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31126</v>
+        <v>20988</v>
       </c>
       <c r="D6" t="n">
-        <v>27760</v>
+        <v>10145</v>
       </c>
       <c r="E6" t="n">
-        <v>31108</v>
+        <v>10145</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8919</v>
+        <v>0.4834000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.4834000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9775</v>
+        <v>0.9555</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7086</v>
+        <v>5902</v>
       </c>
       <c r="D7" t="n">
-        <v>6975</v>
+        <v>651</v>
       </c>
       <c r="E7" t="n">
-        <v>7033</v>
+        <v>651</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9843000000000001</v>
+        <v>0.1103</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9925</v>
+        <v>0.1103</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7181000000000001</v>
+        <v>0.6355</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6817</v>
+        <v>6152</v>
       </c>
       <c r="D8" t="n">
-        <v>6386</v>
+        <v>1160</v>
       </c>
       <c r="E8" t="n">
-        <v>6386</v>
+        <v>1160</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9368000000000001</v>
+        <v>0.1886</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9368000000000001</v>
+        <v>0.1886</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8729</v>
+        <v>0.7238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,26 +701,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1370</v>
+        <v>765</v>
       </c>
       <c r="D10" t="n">
-        <v>1313</v>
+        <v>430</v>
       </c>
       <c r="E10" t="n">
-        <v>1314</v>
+        <v>430</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9584</v>
+        <v>0.5621</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9591</v>
+        <v>0.5621</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9579000000000001</v>
+        <v>0.8845999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -759,20 +757,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
@@ -780,7 +774,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -804,7 +798,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -813,28 +807,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2394</v>
+        <v>1494</v>
       </c>
       <c r="D13" t="n">
-        <v>2268</v>
+        <v>308</v>
       </c>
       <c r="E13" t="n">
-        <v>2386</v>
+        <v>308</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9473999999999999</v>
+        <v>0.2062</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9967</v>
+        <v>0.2062</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9153</v>
+        <v>0.8173999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -843,28 +837,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10703</v>
+        <v>8040</v>
       </c>
       <c r="D14" t="n">
-        <v>10024</v>
+        <v>1430</v>
       </c>
       <c r="E14" t="n">
-        <v>10611</v>
+        <v>1430</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9366</v>
+        <v>0.1779</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9914000000000001</v>
+        <v>0.1779</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9151</v>
+        <v>0.8628</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Taxa de Coleta no Prazo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa de Coleta no Prazo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coleta no Prazo'!$A$1:$H$15</definedName>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1468</v>
+        <v>1833</v>
       </c>
       <c r="D3" t="n">
-        <v>481</v>
+        <v>1697</v>
       </c>
       <c r="E3" t="n">
-        <v>481</v>
+        <v>1768</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.3277</v>
+        <v>0.9258</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.3277</v>
+        <v>0.9645</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9135</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13395</v>
+        <v>15984</v>
       </c>
       <c r="D4" t="n">
-        <v>2280</v>
+        <v>13032</v>
       </c>
       <c r="E4" t="n">
-        <v>2280</v>
+        <v>15515</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1702</v>
+        <v>0.8153</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1702</v>
+        <v>0.9706999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8434999999999999</v>
+        <v>0.8708</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20988</v>
+        <v>30125</v>
       </c>
       <c r="D6" t="n">
-        <v>10145</v>
+        <v>28389</v>
       </c>
       <c r="E6" t="n">
-        <v>10145</v>
+        <v>29924</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.4834000000000001</v>
+        <v>0.9423999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.4834000000000001</v>
+        <v>0.9933</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9555</v>
+        <v>0.9611</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5902</v>
+        <v>7262</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>4802</v>
       </c>
       <c r="E7" t="n">
-        <v>651</v>
+        <v>6944</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1103</v>
+        <v>0.6613</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1103</v>
+        <v>0.9562</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6355</v>
+        <v>0.5885</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6152</v>
+        <v>6379</v>
       </c>
       <c r="D8" t="n">
-        <v>1160</v>
+        <v>5100</v>
       </c>
       <c r="E8" t="n">
-        <v>1160</v>
+        <v>5100</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1886</v>
+        <v>0.7995</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1886</v>
+        <v>0.7995</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7238</v>
+        <v>0.7121999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,16 +701,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -718,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>765</v>
+        <v>1555</v>
       </c>
       <c r="D10" t="n">
-        <v>430</v>
+        <v>1347</v>
       </c>
       <c r="E10" t="n">
-        <v>430</v>
+        <v>1361</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.5621</v>
+        <v>0.8662000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.5621</v>
+        <v>0.8752</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8845999999999999</v>
+        <v>0.8854000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,16 +761,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="3" t="n"/>
+        <v>77</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
@@ -774,7 +782,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -798,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -807,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1494</v>
+        <v>9280</v>
       </c>
       <c r="D13" t="n">
-        <v>308</v>
+        <v>8846</v>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>9107</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.2062</v>
+        <v>0.9531999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.2062</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8173999999999999</v>
+        <v>0.8597</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -837,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8040</v>
+        <v>9427</v>
       </c>
       <c r="D14" t="n">
-        <v>1430</v>
+        <v>8049</v>
       </c>
       <c r="E14" t="n">
-        <v>1430</v>
+        <v>8147</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.1779</v>
+        <v>0.8538</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.1779</v>
+        <v>0.8642</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8628</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.3277</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9135</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.1702</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8434999999999999</v>
+        <v>0.8465</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.4834000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9555</v>
+        <v>0.9466</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.1103</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6355</v>
+        <v>0.6061</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.1886</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7238</v>
+        <v>0.6441</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.5621</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8845999999999999</v>
+        <v>0.8782</v>
       </c>
     </row>
     <row r="11">
@@ -822,7 +822,7 @@
         <v>0.2062</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8173999999999999</v>
+        <v>0.8487</v>
       </c>
     </row>
     <row r="14">
@@ -852,7 +852,7 @@
         <v>0.1779</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8628</v>
+        <v>0.8734000000000001</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1468</v>
+        <v>1386</v>
       </c>
       <c r="D3" t="n">
-        <v>481</v>
+        <v>1311</v>
       </c>
       <c r="E3" t="n">
-        <v>481</v>
+        <v>1361</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.3277</v>
+        <v>0.9459000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.3277</v>
+        <v>0.982</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.9223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13395</v>
+        <v>15709</v>
       </c>
       <c r="D4" t="n">
-        <v>2280</v>
+        <v>11053</v>
       </c>
       <c r="E4" t="n">
-        <v>2280</v>
+        <v>15430</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1702</v>
+        <v>0.7036</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1702</v>
+        <v>0.9822</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8465</v>
+        <v>0.8556999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20988</v>
+        <v>33014</v>
       </c>
       <c r="D6" t="n">
-        <v>10145</v>
+        <v>25228</v>
       </c>
       <c r="E6" t="n">
-        <v>10145</v>
+        <v>32277</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.4834000000000001</v>
+        <v>0.7642</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.4834000000000001</v>
+        <v>0.9777</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9466</v>
+        <v>0.9767</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5902</v>
+        <v>5935</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>2755</v>
       </c>
       <c r="E7" t="n">
-        <v>651</v>
+        <v>5846</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1103</v>
+        <v>0.4642</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1103</v>
+        <v>0.985</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6061</v>
+        <v>0.6848000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6152</v>
+        <v>7275</v>
       </c>
       <c r="D8" t="n">
-        <v>1160</v>
+        <v>5357</v>
       </c>
       <c r="E8" t="n">
-        <v>1160</v>
+        <v>7228</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1886</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1886</v>
+        <v>0.9934999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6441</v>
+        <v>0.7134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,16 +701,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -718,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>765</v>
+        <v>1484</v>
       </c>
       <c r="D10" t="n">
-        <v>430</v>
+        <v>1106</v>
       </c>
       <c r="E10" t="n">
-        <v>430</v>
+        <v>1144</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.5621</v>
+        <v>0.7453</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.5621</v>
+        <v>0.7709</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8782</v>
+        <v>0.7920999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,16 +761,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="3" t="n"/>
+        <v>72</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
@@ -774,7 +782,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -798,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -807,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1494</v>
+        <v>973</v>
       </c>
       <c r="D13" t="n">
-        <v>308</v>
+        <v>800</v>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>926</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.2062</v>
+        <v>0.8222</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.2062</v>
+        <v>0.9517</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8487</v>
+        <v>0.8387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -837,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8040</v>
+        <v>8366</v>
       </c>
       <c r="D14" t="n">
-        <v>1430</v>
+        <v>6803</v>
       </c>
       <c r="E14" t="n">
-        <v>1430</v>
+        <v>8139</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.1779</v>
+        <v>0.8131999999999999</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.1779</v>
+        <v>0.9729000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8734000000000001</v>
+        <v>0.9012</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.982</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9223</v>
+        <v>0.9104000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9822</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8556999999999999</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9777</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9754</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.985</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6848000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9934999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7134</v>
+        <v>0.7931</v>
       </c>
     </row>
     <row r="9">
@@ -746,7 +746,7 @@
         <v>0.7709</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.7920999999999999</v>
+        <v>0.7977</v>
       </c>
     </row>
     <row r="11">
@@ -830,7 +830,7 @@
         <v>0.9517</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8387</v>
+        <v>0.8583</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +860,7 @@
         <v>0.9729000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9012</v>
+        <v>0.8803</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1386</v>
+        <v>3188</v>
       </c>
       <c r="D3" t="n">
-        <v>1311</v>
+        <v>2924</v>
       </c>
       <c r="E3" t="n">
-        <v>1361</v>
+        <v>3131</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9459000000000001</v>
+        <v>0.9172</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.982</v>
+        <v>0.9821</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9104000000000001</v>
+        <v>0.9465</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15709</v>
+        <v>26444</v>
       </c>
       <c r="D4" t="n">
-        <v>11053</v>
+        <v>22976</v>
       </c>
       <c r="E4" t="n">
-        <v>15430</v>
+        <v>26313</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7036</v>
+        <v>0.8689</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9822</v>
+        <v>0.995</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.847</v>
+        <v>0.8826999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33014</v>
+        <v>38906</v>
       </c>
       <c r="D6" t="n">
-        <v>25228</v>
+        <v>34297</v>
       </c>
       <c r="E6" t="n">
-        <v>32277</v>
+        <v>38152</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7642</v>
+        <v>0.8815000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>0.9806</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>0.9777</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.9754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5935</v>
+        <v>7127</v>
       </c>
       <c r="D7" t="n">
-        <v>2755</v>
+        <v>5236</v>
       </c>
       <c r="E7" t="n">
-        <v>5846</v>
+        <v>7101</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4642</v>
+        <v>0.7347</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.985</v>
+        <v>0.9964</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7584000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7275</v>
+        <v>7649</v>
       </c>
       <c r="D8" t="n">
-        <v>5357</v>
+        <v>6526</v>
       </c>
       <c r="E8" t="n">
-        <v>7228</v>
+        <v>6526</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.8532</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9934999999999999</v>
+        <v>0.8532</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7931</v>
+        <v>0.9031999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1484</v>
+        <v>3980</v>
       </c>
       <c r="D10" t="n">
-        <v>1106</v>
+        <v>3438</v>
       </c>
       <c r="E10" t="n">
-        <v>1144</v>
+        <v>3627</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7453</v>
+        <v>0.8637999999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.7709</v>
+        <v>0.9113</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.7977</v>
+        <v>0.9505</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>72</v>
+        <v>573</v>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>573</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>573</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -782,7 +782,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>973</v>
+        <v>12174</v>
       </c>
       <c r="D13" t="n">
-        <v>800</v>
+        <v>11876</v>
       </c>
       <c r="E13" t="n">
-        <v>926</v>
+        <v>12139</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.8222</v>
+        <v>0.9754999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9517</v>
+        <v>0.9971</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8583</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8366</v>
+        <v>14978</v>
       </c>
       <c r="D14" t="n">
-        <v>6803</v>
+        <v>13504</v>
       </c>
       <c r="E14" t="n">
-        <v>8139</v>
+        <v>14811</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8131999999999999</v>
+        <v>0.9016</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9729000000000001</v>
+        <v>0.9889</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8803</v>
+        <v>0.9579000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9821</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9465</v>
+        <v>0.9712999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.995</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8826999999999999</v>
+        <v>0.8951</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9806</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9777</v>
+        <v>0.9829000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9964</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7584000000000001</v>
+        <v>0.7619</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.8532</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9031999999999999</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="9">
@@ -746,7 +746,7 @@
         <v>0.9113</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9505</v>
+        <v>0.9577</v>
       </c>
     </row>
     <row r="11">
@@ -830,7 +830,7 @@
         <v>0.9971</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9125</v>
+        <v>0.9228000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +860,7 @@
         <v>0.9889</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9579000000000001</v>
+        <v>0.9556</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3188</v>
+        <v>2092</v>
       </c>
       <c r="D3" t="n">
-        <v>2924</v>
+        <v>2027</v>
       </c>
       <c r="E3" t="n">
-        <v>3131</v>
+        <v>2040</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9172</v>
+        <v>0.9689</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9821</v>
+        <v>0.9751000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9712999999999999</v>
+        <v>0.9462</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26444</v>
+        <v>26079</v>
       </c>
       <c r="D4" t="n">
-        <v>22976</v>
+        <v>21546</v>
       </c>
       <c r="E4" t="n">
-        <v>26313</v>
+        <v>23835</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8689</v>
+        <v>0.8262</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.995</v>
+        <v>0.914</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8951</v>
+        <v>0.8709</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38906</v>
+        <v>42739</v>
       </c>
       <c r="D6" t="n">
-        <v>34297</v>
+        <v>37078</v>
       </c>
       <c r="E6" t="n">
-        <v>38152</v>
+        <v>38655</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8675</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9806</v>
+        <v>0.9044</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9829000000000001</v>
+        <v>0.9887999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7127</v>
+        <v>7253</v>
       </c>
       <c r="D7" t="n">
-        <v>5236</v>
+        <v>5760</v>
       </c>
       <c r="E7" t="n">
-        <v>7101</v>
+        <v>6607</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7347</v>
+        <v>0.7942</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9964</v>
+        <v>0.9109</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7619</v>
+        <v>0.7881999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7649</v>
+        <v>8189</v>
       </c>
       <c r="D8" t="n">
-        <v>6526</v>
+        <v>6842</v>
       </c>
       <c r="E8" t="n">
-        <v>6526</v>
+        <v>6842</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8532</v>
+        <v>0.8355</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8532</v>
+        <v>0.8355</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8903</v>
+        <v>0.9264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3980</v>
+        <v>3797</v>
       </c>
       <c r="D10" t="n">
-        <v>3438</v>
+        <v>3684</v>
       </c>
       <c r="E10" t="n">
-        <v>3627</v>
+        <v>3693</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8637999999999999</v>
+        <v>0.9702</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9113</v>
+        <v>0.9726</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9577</v>
+        <v>0.9640000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>573</v>
+        <v>645</v>
       </c>
       <c r="D11" t="n">
-        <v>573</v>
+        <v>645</v>
       </c>
       <c r="E11" t="n">
-        <v>573</v>
+        <v>645</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -782,7 +782,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12174</v>
+        <v>5290</v>
       </c>
       <c r="D13" t="n">
-        <v>11876</v>
+        <v>5178</v>
       </c>
       <c r="E13" t="n">
-        <v>12139</v>
+        <v>5267</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9754999999999999</v>
+        <v>0.9788</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9971</v>
+        <v>0.9956999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9228000000000001</v>
+        <v>0.9207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14978</v>
+        <v>12452</v>
       </c>
       <c r="D14" t="n">
-        <v>13504</v>
+        <v>11809</v>
       </c>
       <c r="E14" t="n">
-        <v>14811</v>
+        <v>11869</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9016</v>
+        <v>0.9484</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9889</v>
+        <v>0.9531999999999999</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9556</v>
+        <v>0.9606</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9751000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9462</v>
+        <v>0.9506999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.914</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8709</v>
+        <v>0.8811</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9044</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9887999999999999</v>
+        <v>0.9863</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9109</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7881999999999999</v>
+        <v>0.7655</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.8355</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9264</v>
+        <v>0.9006000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -746,7 +746,7 @@
         <v>0.9726</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9640000000000001</v>
+        <v>0.9634999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -830,7 +830,7 @@
         <v>0.9956999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9207</v>
+        <v>0.9356</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +860,7 @@
         <v>0.9531999999999999</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9606</v>
+        <v>0.9573</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2092</v>
+        <v>2157</v>
       </c>
       <c r="D3" t="n">
-        <v>2027</v>
+        <v>2141</v>
       </c>
       <c r="E3" t="n">
-        <v>2040</v>
+        <v>2156</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9689</v>
+        <v>0.9926</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9751000000000001</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9506999999999999</v>
+        <v>0.9359999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26079</v>
+        <v>26866</v>
       </c>
       <c r="D4" t="n">
-        <v>21546</v>
+        <v>25345</v>
       </c>
       <c r="E4" t="n">
-        <v>23835</v>
+        <v>26561</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8262</v>
+        <v>0.9434</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.914</v>
+        <v>0.9886</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8811</v>
+        <v>0.8974</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>42739</v>
+        <v>39044</v>
       </c>
       <c r="D6" t="n">
-        <v>37078</v>
+        <v>34059</v>
       </c>
       <c r="E6" t="n">
-        <v>38655</v>
+        <v>38925</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8675</v>
+        <v>0.8723000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9044</v>
+        <v>0.997</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9863</v>
+        <v>0.9818000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7253</v>
+        <v>8323</v>
       </c>
       <c r="D7" t="n">
-        <v>5760</v>
+        <v>7085</v>
       </c>
       <c r="E7" t="n">
-        <v>6607</v>
+        <v>8314</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7942</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9109</v>
+        <v>0.9989</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7655</v>
+        <v>0.6940000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8189</v>
+        <v>8266</v>
       </c>
       <c r="D8" t="n">
-        <v>6842</v>
+        <v>7336</v>
       </c>
       <c r="E8" t="n">
-        <v>6842</v>
+        <v>8230</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8355</v>
+        <v>0.8875</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8355</v>
+        <v>0.9956</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9006000000000001</v>
+        <v>0.8659</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,20 +701,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -722,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3797</v>
+        <v>3624</v>
       </c>
       <c r="D10" t="n">
-        <v>3684</v>
+        <v>3436</v>
       </c>
       <c r="E10" t="n">
-        <v>3693</v>
+        <v>3531</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9702</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9726</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9634999999999999</v>
+        <v>0.9808</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +757,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>645</v>
+        <v>235</v>
       </c>
       <c r="D11" t="n">
-        <v>645</v>
+        <v>235</v>
       </c>
       <c r="E11" t="n">
-        <v>645</v>
+        <v>235</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -782,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +802,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +811,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5290</v>
+        <v>9794</v>
       </c>
       <c r="D13" t="n">
-        <v>5178</v>
+        <v>9614</v>
       </c>
       <c r="E13" t="n">
-        <v>5267</v>
+        <v>9791</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9788</v>
+        <v>0.9815999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9956999999999999</v>
+        <v>0.9997</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9356</v>
+        <v>0.9670000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +841,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12452</v>
+        <v>10552</v>
       </c>
       <c r="D14" t="n">
-        <v>11809</v>
+        <v>10172</v>
       </c>
       <c r="E14" t="n">
-        <v>11869</v>
+        <v>10455</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9484</v>
+        <v>0.9640000000000001</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9531999999999999</v>
+        <v>0.9908</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9573</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9995000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9359999999999999</v>
+        <v>0.9381</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9886</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8974</v>
+        <v>0.8765999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.997</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9818000000000001</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9989</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6940000000000001</v>
+        <v>0.7153</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9956</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8659</v>
+        <v>0.9012</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.9743000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9808</v>
+        <v>0.9761</v>
       </c>
     </row>
     <row r="11">
@@ -826,7 +826,7 @@
         <v>0.9997</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9670000000000001</v>
+        <v>0.9784</v>
       </c>
     </row>
     <row r="14">
@@ -856,7 +856,7 @@
         <v>0.9908</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.963</v>
+        <v>0.9556999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2157</v>
+        <v>1788</v>
       </c>
       <c r="D3" t="n">
-        <v>2141</v>
+        <v>1775</v>
       </c>
       <c r="E3" t="n">
-        <v>2156</v>
+        <v>1787</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9926</v>
+        <v>0.9926999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9381</v>
+        <v>0.9126000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26866</v>
+        <v>25252</v>
       </c>
       <c r="D4" t="n">
-        <v>25345</v>
+        <v>23211</v>
       </c>
       <c r="E4" t="n">
-        <v>26561</v>
+        <v>23511</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9434</v>
+        <v>0.9192</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9886</v>
+        <v>0.9311</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8765999999999999</v>
+        <v>0.9488</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39044</v>
+        <v>33209</v>
       </c>
       <c r="D6" t="n">
-        <v>34059</v>
+        <v>30200</v>
       </c>
       <c r="E6" t="n">
-        <v>38925</v>
+        <v>33086</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8723000000000001</v>
+        <v>0.9094</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.997</v>
+        <v>0.9963</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9771</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8323</v>
+        <v>5052</v>
       </c>
       <c r="D7" t="n">
-        <v>7085</v>
+        <v>3894</v>
       </c>
       <c r="E7" t="n">
-        <v>8314</v>
+        <v>3894</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.7707999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9989</v>
+        <v>0.7707999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7153</v>
+        <v>0.4691</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8266</v>
+        <v>6813</v>
       </c>
       <c r="D8" t="n">
-        <v>7336</v>
+        <v>6152</v>
       </c>
       <c r="E8" t="n">
-        <v>8230</v>
+        <v>6152</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8875</v>
+        <v>0.903</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9956</v>
+        <v>0.903</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9012</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,16 +701,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -718,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3624</v>
+        <v>3925</v>
       </c>
       <c r="D10" t="n">
-        <v>3436</v>
+        <v>3762</v>
       </c>
       <c r="E10" t="n">
-        <v>3531</v>
+        <v>3766</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9584999999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9595</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9761</v>
+        <v>0.9728</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="E11" t="n">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -772,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>0.9639</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -802,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9794</v>
+        <v>9098</v>
       </c>
       <c r="D13" t="n">
-        <v>9614</v>
+        <v>8788</v>
       </c>
       <c r="E13" t="n">
-        <v>9791</v>
+        <v>9098</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9815999999999999</v>
+        <v>0.9659</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9784</v>
+        <v>0.9612999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10552</v>
+        <v>9622</v>
       </c>
       <c r="D14" t="n">
-        <v>10172</v>
+        <v>9158</v>
       </c>
       <c r="E14" t="n">
-        <v>10455</v>
+        <v>9555</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9640000000000001</v>
+        <v>0.9518000000000001</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9908</v>
+        <v>0.993</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9556999999999999</v>
+        <v>0.9838</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9994</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9126000000000001</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9311</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9488</v>
+        <v>0.9501999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9963</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9667</v>
+        <v>0.9781</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.7707999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4691</v>
+        <v>0.5556</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.903</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.88</v>
+        <v>0.9255</v>
       </c>
     </row>
     <row r="9">
@@ -746,7 +746,7 @@
         <v>0.9595</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9728</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9639</v>
+        <v>0.9732999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -830,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9612999999999999</v>
+        <v>0.9773999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +860,7 @@
         <v>0.993</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9838</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="15">
@@ -885,7 +885,9 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H15"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1788</v>
+        <v>1688</v>
       </c>
       <c r="D3" t="n">
-        <v>1775</v>
+        <v>1479</v>
       </c>
       <c r="E3" t="n">
-        <v>1787</v>
+        <v>1605</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9926999999999999</v>
+        <v>0.8762000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.9508</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9706999999999999</v>
+        <v>0.9439</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25252</v>
+        <v>20006</v>
       </c>
       <c r="D4" t="n">
-        <v>23211</v>
+        <v>17319</v>
       </c>
       <c r="E4" t="n">
-        <v>23511</v>
+        <v>18127</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9192</v>
+        <v>0.8656999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9311</v>
+        <v>0.9061</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9501999999999999</v>
+        <v>0.9593</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33209</v>
+        <v>30291</v>
       </c>
       <c r="D6" t="n">
-        <v>30200</v>
+        <v>25088</v>
       </c>
       <c r="E6" t="n">
-        <v>33086</v>
+        <v>25921</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9094</v>
+        <v>0.8281999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9963</v>
+        <v>0.8556999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9781</v>
+        <v>0.9738</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5052</v>
+        <v>5335</v>
       </c>
       <c r="D7" t="n">
-        <v>3894</v>
+        <v>1602</v>
       </c>
       <c r="E7" t="n">
-        <v>3894</v>
+        <v>5194</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7707999999999999</v>
+        <v>0.3003</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.7707999999999999</v>
+        <v>0.9736</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5556</v>
+        <v>0.4921</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6813</v>
+        <v>7290</v>
       </c>
       <c r="D8" t="n">
-        <v>6152</v>
+        <v>5899</v>
       </c>
       <c r="E8" t="n">
-        <v>6152</v>
+        <v>5899</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.903</v>
+        <v>0.8092</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.903</v>
+        <v>0.8092</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9255</v>
+        <v>0.8902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3925</v>
+        <v>3469</v>
       </c>
       <c r="D10" t="n">
-        <v>3762</v>
+        <v>2990</v>
       </c>
       <c r="E10" t="n">
-        <v>3766</v>
+        <v>3023</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9584999999999999</v>
+        <v>0.8619</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9595</v>
+        <v>0.8714</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9706999999999999</v>
+        <v>0.9753000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="E11" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9732999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9098</v>
+        <v>9717</v>
       </c>
       <c r="D13" t="n">
-        <v>8788</v>
+        <v>8995</v>
       </c>
       <c r="E13" t="n">
-        <v>9098</v>
+        <v>9673</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9659</v>
+        <v>0.9257</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>0.9954999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9773999999999999</v>
+        <v>0.9815</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9622</v>
+        <v>9691</v>
       </c>
       <c r="D14" t="n">
-        <v>9158</v>
+        <v>8278</v>
       </c>
       <c r="E14" t="n">
-        <v>9555</v>
+        <v>8705</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9518000000000001</v>
+        <v>0.8542000000000001</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.993</v>
+        <v>0.8983</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9756</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9508</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9439</v>
+        <v>0.9505</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9061</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9593</v>
+        <v>0.9440999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.8556999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9738</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9736</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4921</v>
+        <v>0.4902</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.8092</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8902</v>
+        <v>0.8951</v>
       </c>
     </row>
     <row r="9">
@@ -746,7 +746,7 @@
         <v>0.8714</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9753000000000001</v>
+        <v>0.9845</v>
       </c>
     </row>
     <row r="11">
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>0.9412</v>
       </c>
     </row>
     <row r="12">
@@ -830,7 +830,7 @@
         <v>0.9954999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9815</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +860,7 @@
         <v>0.8983</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9773000000000001</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1688</v>
+        <v>1896</v>
       </c>
       <c r="D3" t="n">
-        <v>1479</v>
+        <v>338</v>
       </c>
       <c r="E3" t="n">
-        <v>1605</v>
+        <v>338</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8762000000000001</v>
+        <v>0.1783</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9508</v>
+        <v>0.1783</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9505</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20006</v>
+        <v>16674</v>
       </c>
       <c r="D4" t="n">
-        <v>17319</v>
+        <v>4437</v>
       </c>
       <c r="E4" t="n">
-        <v>18127</v>
+        <v>4437</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8656999999999999</v>
+        <v>0.2661</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9061</v>
+        <v>0.2661</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9440999999999999</v>
+        <v>0.9447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30291</v>
+        <v>31993</v>
       </c>
       <c r="D6" t="n">
-        <v>25088</v>
+        <v>15759</v>
       </c>
       <c r="E6" t="n">
-        <v>25921</v>
+        <v>15759</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8281999999999999</v>
+        <v>0.4926</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.8556999999999999</v>
+        <v>0.4926</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9771</v>
+        <v>0.9692000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5335</v>
+        <v>4942</v>
       </c>
       <c r="D7" t="n">
-        <v>1602</v>
+        <v>404</v>
       </c>
       <c r="E7" t="n">
-        <v>5194</v>
+        <v>404</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3003</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9736</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4902</v>
+        <v>0.6545000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7290</v>
+        <v>7416</v>
       </c>
       <c r="D8" t="n">
-        <v>5899</v>
+        <v>1997</v>
       </c>
       <c r="E8" t="n">
-        <v>5899</v>
+        <v>1997</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8092</v>
+        <v>0.2693</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8092</v>
+        <v>0.2693</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8951</v>
+        <v>0.9103</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,20 +701,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -722,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3469</v>
+        <v>2879</v>
       </c>
       <c r="D10" t="n">
-        <v>2990</v>
+        <v>710</v>
       </c>
       <c r="E10" t="n">
-        <v>3023</v>
+        <v>710</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8619</v>
+        <v>0.2466</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8714</v>
+        <v>0.2466</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9845</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +757,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,13 +772,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9412</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +802,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +811,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9717</v>
+        <v>5362</v>
       </c>
       <c r="D13" t="n">
-        <v>8995</v>
+        <v>490</v>
       </c>
       <c r="E13" t="n">
-        <v>9673</v>
+        <v>490</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9257</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9954999999999999</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9745</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +841,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9691</v>
+        <v>9573</v>
       </c>
       <c r="D14" t="n">
-        <v>8278</v>
+        <v>2006</v>
       </c>
       <c r="E14" t="n">
-        <v>8705</v>
+        <v>2006</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8542000000000001</v>
+        <v>0.2095</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.8983</v>
+        <v>0.2095</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9773000000000001</v>
+        <v>0.9651999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.1783</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9465</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.2661</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9447</v>
+        <v>0.9456</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.4926</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9692000000000001</v>
+        <v>0.9818000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6545000000000001</v>
+        <v>0.6175999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.2693</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9103</v>
+        <v>0.8909</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.2466</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9795</v>
+        <v>0.9892</v>
       </c>
     </row>
     <row r="11">
@@ -772,7 +772,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9667</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="12">
@@ -826,7 +826,7 @@
         <v>0.09140000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.963</v>
+        <v>0.9390000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -856,7 +856,7 @@
         <v>0.2095</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9704999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -881,9 +881,7 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H15" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H15"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1896</v>
+        <v>2406</v>
       </c>
       <c r="D3" t="n">
-        <v>338</v>
+        <v>574</v>
       </c>
       <c r="E3" t="n">
-        <v>338</v>
+        <v>574</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.1783</v>
+        <v>0.2386</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1783</v>
+        <v>0.2386</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9465</v>
+        <v>0.9317</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16674</v>
+        <v>14209</v>
       </c>
       <c r="D4" t="n">
-        <v>4437</v>
+        <v>1420</v>
       </c>
       <c r="E4" t="n">
-        <v>4437</v>
+        <v>1420</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.2661</v>
+        <v>0.0999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.2661</v>
+        <v>0.0999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9456</v>
+        <v>0.8976999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31993</v>
+        <v>37041</v>
       </c>
       <c r="D6" t="n">
-        <v>15759</v>
+        <v>20806</v>
       </c>
       <c r="E6" t="n">
-        <v>15759</v>
+        <v>20806</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.4926</v>
+        <v>0.5617</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.4926</v>
+        <v>0.5617</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9818000000000001</v>
+        <v>0.9409000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4942</v>
+        <v>5740</v>
       </c>
       <c r="D7" t="n">
-        <v>404</v>
+        <v>714</v>
       </c>
       <c r="E7" t="n">
-        <v>404</v>
+        <v>714</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.1244</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.1244</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6175999999999999</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7416</v>
+        <v>6594</v>
       </c>
       <c r="D8" t="n">
-        <v>1997</v>
+        <v>630</v>
       </c>
       <c r="E8" t="n">
-        <v>1997</v>
+        <v>630</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.2693</v>
+        <v>0.0955</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.2693</v>
+        <v>0.0955</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8909</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2879</v>
+        <v>4991</v>
       </c>
       <c r="D10" t="n">
-        <v>710</v>
+        <v>1225</v>
       </c>
       <c r="E10" t="n">
-        <v>710</v>
+        <v>1225</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.2466</v>
+        <v>0.2454</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.2466</v>
+        <v>0.2454</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9892</v>
+        <v>0.9529000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,28 +757,24 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.9231</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -802,7 +798,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,28 +807,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5362</v>
+        <v>7702</v>
       </c>
       <c r="D13" t="n">
-        <v>490</v>
+        <v>3706</v>
       </c>
       <c r="E13" t="n">
-        <v>490</v>
+        <v>3706</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.09140000000000001</v>
+        <v>0.4812</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.09140000000000001</v>
+        <v>0.4812</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9390000000000001</v>
+        <v>0.9308</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,28 +837,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9573</v>
+        <v>9239</v>
       </c>
       <c r="D14" t="n">
-        <v>2006</v>
+        <v>510</v>
       </c>
       <c r="E14" t="n">
-        <v>2006</v>
+        <v>510</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.2095</v>
+        <v>0.0552</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2095</v>
+        <v>0.0552</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9704999999999999</v>
+        <v>0.9521999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.2386</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9317</v>
+        <v>0.9548000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.0999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8976999999999999</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.5617</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9409000000000001</v>
+        <v>0.9286</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.1244</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5455</v>
+        <v>0.6071</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.0955</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.875</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.2454</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9529000000000001</v>
+        <v>0.9648</v>
       </c>
     </row>
     <row r="11">
@@ -822,7 +822,7 @@
         <v>0.4812</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9308</v>
+        <v>0.9349</v>
       </c>
     </row>
     <row r="14">
@@ -852,7 +852,7 @@
         <v>0.0552</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9521999999999999</v>
+        <v>0.9631000000000001</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2406</v>
+        <v>3356</v>
       </c>
       <c r="D3" t="n">
-        <v>574</v>
+        <v>2322</v>
       </c>
       <c r="E3" t="n">
-        <v>574</v>
+        <v>2859</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2386</v>
+        <v>0.6919</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2386</v>
+        <v>0.8519</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9548000000000001</v>
+        <v>0.8401999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14209</v>
+        <v>25590</v>
       </c>
       <c r="D4" t="n">
-        <v>1420</v>
+        <v>16867</v>
       </c>
       <c r="E4" t="n">
-        <v>1420</v>
+        <v>24203</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0999</v>
+        <v>0.6591</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.0999</v>
+        <v>0.9458</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8944</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37041</v>
+        <v>41662</v>
       </c>
       <c r="D6" t="n">
-        <v>20806</v>
+        <v>26820</v>
       </c>
       <c r="E6" t="n">
-        <v>20806</v>
+        <v>32453</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.5617</v>
+        <v>0.6437999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5617</v>
+        <v>0.779</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9286</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5740</v>
+        <v>6862</v>
       </c>
       <c r="D7" t="n">
-        <v>714</v>
+        <v>1308</v>
       </c>
       <c r="E7" t="n">
-        <v>714</v>
+        <v>6843</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1244</v>
+        <v>0.1906</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1244</v>
+        <v>0.9972</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6071</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6594</v>
+        <v>8437</v>
       </c>
       <c r="D8" t="n">
-        <v>630</v>
+        <v>3735</v>
       </c>
       <c r="E8" t="n">
-        <v>630</v>
+        <v>3735</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.0955</v>
+        <v>0.4427</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.0955</v>
+        <v>0.4427</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.903</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4991</v>
+        <v>5039</v>
       </c>
       <c r="D10" t="n">
-        <v>1225</v>
+        <v>4043</v>
       </c>
       <c r="E10" t="n">
-        <v>1225</v>
+        <v>4217</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.2454</v>
+        <v>0.8023</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.2454</v>
+        <v>0.8369</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9648</v>
+        <v>0.9634</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,16 +757,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="3" t="n"/>
+        <v>168</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
@@ -774,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -798,7 +802,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -807,28 +811,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7702</v>
+        <v>9706</v>
       </c>
       <c r="D13" t="n">
-        <v>3706</v>
+        <v>2006</v>
       </c>
       <c r="E13" t="n">
-        <v>3706</v>
+        <v>9384</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.4812</v>
+        <v>0.2067</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.4812</v>
+        <v>0.9668000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9349</v>
+        <v>0.8889</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -837,28 +841,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9239</v>
+        <v>14995</v>
       </c>
       <c r="D14" t="n">
-        <v>510</v>
+        <v>11170</v>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>14709</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.0552</v>
+        <v>0.7448999999999999</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.0552</v>
+        <v>0.9809</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9631000000000001</v>
+        <v>0.9276000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.8519</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.8431000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9458</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.904</v>
+        <v>0.9109999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.779</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9759</v>
+        <v>0.9793999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9972</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.625</v>
+        <v>0.7826000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.4427</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.875</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.8369</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9634</v>
+        <v>0.9509000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -826,7 +826,7 @@
         <v>0.9668000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8889</v>
+        <v>0.8484999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -856,7 +856,7 @@
         <v>0.9809</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9276000000000001</v>
+        <v>0.9316</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3356</v>
+        <v>3209</v>
       </c>
       <c r="D3" t="n">
-        <v>2322</v>
+        <v>2452</v>
       </c>
       <c r="E3" t="n">
-        <v>2859</v>
+        <v>2974</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6919</v>
+        <v>0.7641</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.8519</v>
+        <v>0.9268000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8431000000000001</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25590</v>
+        <v>28308</v>
       </c>
       <c r="D4" t="n">
-        <v>16867</v>
+        <v>24218</v>
       </c>
       <c r="E4" t="n">
-        <v>24203</v>
+        <v>28074</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6591</v>
+        <v>0.8554999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9458</v>
+        <v>0.9917</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9109999999999999</v>
+        <v>0.9392</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41662</v>
+        <v>39098</v>
       </c>
       <c r="D6" t="n">
-        <v>26820</v>
+        <v>30847</v>
       </c>
       <c r="E6" t="n">
-        <v>32453</v>
+        <v>34500</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.6437999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.779</v>
+        <v>0.8824</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9793999999999999</v>
+        <v>0.9812000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6862</v>
+        <v>6749</v>
       </c>
       <c r="D7" t="n">
-        <v>1308</v>
+        <v>2280</v>
       </c>
       <c r="E7" t="n">
-        <v>6843</v>
+        <v>6728</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1906</v>
+        <v>0.3378</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9972</v>
+        <v>0.9969</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7826000000000001</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8437</v>
+        <v>6783</v>
       </c>
       <c r="D8" t="n">
-        <v>3735</v>
+        <v>4956</v>
       </c>
       <c r="E8" t="n">
-        <v>3735</v>
+        <v>4956</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.4427</v>
+        <v>0.7306999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.4427</v>
+        <v>0.7306999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.86</v>
+        <v>0.8704999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5039</v>
+        <v>5387</v>
       </c>
       <c r="D10" t="n">
-        <v>4043</v>
+        <v>5292</v>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>5357</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.9823999999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8369</v>
+        <v>0.9944</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9509000000000001</v>
+        <v>0.9533</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>243</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>243</v>
       </c>
       <c r="E11" t="n">
-        <v>168</v>
+        <v>243</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9706</v>
+        <v>11127</v>
       </c>
       <c r="D13" t="n">
-        <v>2006</v>
+        <v>9573</v>
       </c>
       <c r="E13" t="n">
-        <v>9384</v>
+        <v>11100</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.2067</v>
+        <v>0.8603000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9668000000000001</v>
+        <v>0.9976</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.9487000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,28 +841,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14995</v>
+        <v>12271</v>
       </c>
       <c r="D14" t="n">
-        <v>11170</v>
+        <v>10800</v>
       </c>
       <c r="E14" t="n">
-        <v>14709</v>
+        <v>12034</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.7448999999999999</v>
+        <v>0.8801000000000001</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9809</v>
+        <v>0.9806999999999999</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9316</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9268000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9526</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9917</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9392</v>
+        <v>0.9556</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.8824</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9812000000000001</v>
+        <v>0.9793999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9969</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.76</v>
+        <v>0.8056</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.7306999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8704999999999999</v>
+        <v>0.9253</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.9944</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9533</v>
+        <v>0.9534999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -826,7 +826,7 @@
         <v>0.9976</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9487000000000001</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="14">
@@ -856,7 +856,7 @@
         <v>0.9806999999999999</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9539</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3209</v>
+        <v>2565</v>
       </c>
       <c r="D3" t="n">
-        <v>2452</v>
+        <v>2476</v>
       </c>
       <c r="E3" t="n">
-        <v>2974</v>
+        <v>2543</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.7641</v>
+        <v>0.9653</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9268000000000001</v>
+        <v>0.9914000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9526</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28308</v>
+        <v>23723</v>
       </c>
       <c r="D4" t="n">
-        <v>24218</v>
+        <v>22863</v>
       </c>
       <c r="E4" t="n">
-        <v>28074</v>
+        <v>23293</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8554999999999999</v>
+        <v>0.9637</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9917</v>
+        <v>0.9819</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9556</v>
+        <v>0.9467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39098</v>
+        <v>33840</v>
       </c>
       <c r="D6" t="n">
-        <v>30847</v>
+        <v>24201</v>
       </c>
       <c r="E6" t="n">
-        <v>34500</v>
+        <v>33648</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.789</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.8824</v>
+        <v>0.9943000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9793999999999999</v>
+        <v>0.9767</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6749</v>
+        <v>9045</v>
       </c>
       <c r="D7" t="n">
-        <v>2280</v>
+        <v>2252</v>
       </c>
       <c r="E7" t="n">
-        <v>6728</v>
+        <v>9040</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3378</v>
+        <v>0.249</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9969</v>
+        <v>0.9994</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8056</v>
+        <v>0.7391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6783</v>
+        <v>8323</v>
       </c>
       <c r="D8" t="n">
-        <v>4956</v>
+        <v>6904</v>
       </c>
       <c r="E8" t="n">
-        <v>4956</v>
+        <v>8230</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7306999999999999</v>
+        <v>0.8295</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7306999999999999</v>
+        <v>0.9887999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.9253</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,16 +701,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -718,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5387</v>
+        <v>6035</v>
       </c>
       <c r="D10" t="n">
-        <v>5292</v>
+        <v>5893</v>
       </c>
       <c r="E10" t="n">
-        <v>5357</v>
+        <v>5969</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.9765</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9944</v>
+        <v>0.9891</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9534999999999999</v>
+        <v>0.9594</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="E11" t="n">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -778,7 +782,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -802,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11127</v>
+        <v>3221</v>
       </c>
       <c r="D13" t="n">
-        <v>9573</v>
+        <v>2631</v>
       </c>
       <c r="E13" t="n">
-        <v>11100</v>
+        <v>3190</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.8603000000000001</v>
+        <v>0.8168000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9976</v>
+        <v>0.9904000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9519</v>
+        <v>0.9183</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12271</v>
+        <v>11190</v>
       </c>
       <c r="D14" t="n">
-        <v>10800</v>
+        <v>9802</v>
       </c>
       <c r="E14" t="n">
-        <v>12034</v>
+        <v>10961</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8801000000000001</v>
+        <v>0.8759999999999999</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9806999999999999</v>
+        <v>0.9795</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9539</v>
+        <v>0.9738</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9914000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.904</v>
+        <v>0.8984000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9819</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9467</v>
+        <v>0.9472</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9943000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9761</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9994</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7391</v>
+        <v>0.7955</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9887999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.88</v>
+        <v>0.8643999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -830,7 +830,7 @@
         <v>0.9904000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9183</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +860,7 @@
         <v>0.9795</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9738</v>
+        <v>0.9752</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2565</v>
+        <v>2337</v>
       </c>
       <c r="D3" t="n">
-        <v>2476</v>
+        <v>2298</v>
       </c>
       <c r="E3" t="n">
-        <v>2543</v>
+        <v>2324</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9653</v>
+        <v>0.9833</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9914000000000001</v>
+        <v>0.9944</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8984000000000001</v>
+        <v>0.8842</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23723</v>
+        <v>22312</v>
       </c>
       <c r="D4" t="n">
-        <v>22863</v>
+        <v>20130</v>
       </c>
       <c r="E4" t="n">
-        <v>23293</v>
+        <v>22197</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9637</v>
+        <v>0.9022</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9819</v>
+        <v>0.9948</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9472</v>
+        <v>0.9469</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33840</v>
+        <v>38949</v>
       </c>
       <c r="D6" t="n">
-        <v>24201</v>
+        <v>29670</v>
       </c>
       <c r="E6" t="n">
-        <v>33648</v>
+        <v>32893</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.7618</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9943000000000001</v>
+        <v>0.8445</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9761</v>
+        <v>0.9695</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9045</v>
+        <v>7247</v>
       </c>
       <c r="D7" t="n">
-        <v>2252</v>
+        <v>2561</v>
       </c>
       <c r="E7" t="n">
-        <v>9040</v>
+        <v>7246</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.249</v>
+        <v>0.3534</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7955</v>
+        <v>0.7308</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8323</v>
+        <v>8065</v>
       </c>
       <c r="D8" t="n">
-        <v>6904</v>
+        <v>6520</v>
       </c>
       <c r="E8" t="n">
-        <v>8230</v>
+        <v>8009</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8295</v>
+        <v>0.8084</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9887999999999999</v>
+        <v>0.9931</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,20 +701,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -722,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6035</v>
+        <v>5443</v>
       </c>
       <c r="D10" t="n">
-        <v>5893</v>
+        <v>5354</v>
       </c>
       <c r="E10" t="n">
-        <v>5969</v>
+        <v>5384</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9765</v>
+        <v>0.9836</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9891</v>
+        <v>0.9892</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9594</v>
+        <v>0.9676</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +757,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -782,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +802,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +811,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3221</v>
+        <v>10221</v>
       </c>
       <c r="D13" t="n">
-        <v>2631</v>
+        <v>9834</v>
       </c>
       <c r="E13" t="n">
-        <v>3190</v>
+        <v>10212</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.8168000000000001</v>
+        <v>0.9621</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9904000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.922</v>
+        <v>0.9278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +841,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11190</v>
+        <v>11442</v>
       </c>
       <c r="D14" t="n">
-        <v>9802</v>
+        <v>10921</v>
       </c>
       <c r="E14" t="n">
-        <v>10961</v>
+        <v>11395</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8759999999999999</v>
+        <v>0.9545</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9795</v>
+        <v>0.9959</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9752</v>
+        <v>0.9729000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9944</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8842</v>
+        <v>0.8848999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9948</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9469</v>
+        <v>0.9495</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.8445</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9695</v>
+        <v>0.9731000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7308</v>
+        <v>0.7451000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9931</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8837</v>
+        <v>0.8941</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.9892</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9676</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="11">
@@ -826,7 +826,7 @@
         <v>0.9991</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9278</v>
+        <v>0.9192</v>
       </c>
     </row>
     <row r="14">
@@ -856,7 +856,7 @@
         <v>0.9959</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9729000000000001</v>
+        <v>0.9732</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2337</v>
+        <v>1867</v>
       </c>
       <c r="D3" t="n">
-        <v>2298</v>
+        <v>1520</v>
       </c>
       <c r="E3" t="n">
-        <v>2324</v>
+        <v>1801</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9833</v>
+        <v>0.8140999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9944</v>
+        <v>0.9645999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8848999999999999</v>
+        <v>0.8826000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22312</v>
+        <v>18642</v>
       </c>
       <c r="D4" t="n">
-        <v>20130</v>
+        <v>12073</v>
       </c>
       <c r="E4" t="n">
-        <v>22197</v>
+        <v>17732</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9022</v>
+        <v>0.6476000000000001</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9948</v>
+        <v>0.9512</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9495</v>
+        <v>0.9549</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38949</v>
+        <v>33173</v>
       </c>
       <c r="D6" t="n">
-        <v>29670</v>
+        <v>22126</v>
       </c>
       <c r="E6" t="n">
-        <v>32893</v>
+        <v>32425</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7618</v>
+        <v>0.667</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.8445</v>
+        <v>0.9775</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9731000000000001</v>
+        <v>0.9671999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7247</v>
+        <v>5045</v>
       </c>
       <c r="D7" t="n">
-        <v>2561</v>
+        <v>1699</v>
       </c>
       <c r="E7" t="n">
-        <v>7246</v>
+        <v>1705</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3534</v>
+        <v>0.3368</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.338</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7451000000000001</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8065</v>
+        <v>7717</v>
       </c>
       <c r="D8" t="n">
-        <v>6520</v>
+        <v>5463</v>
       </c>
       <c r="E8" t="n">
-        <v>8009</v>
+        <v>7618</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8084</v>
+        <v>0.7079000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9931</v>
+        <v>0.9872</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8941</v>
+        <v>0.8895000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5443</v>
+        <v>4339</v>
       </c>
       <c r="D10" t="n">
-        <v>5354</v>
+        <v>3318</v>
       </c>
       <c r="E10" t="n">
-        <v>5384</v>
+        <v>4109</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9836</v>
+        <v>0.7646999999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9892</v>
+        <v>0.9470000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9671</v>
+        <v>0.9661</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10221</v>
+        <v>5465</v>
       </c>
       <c r="D13" t="n">
-        <v>9834</v>
+        <v>4468</v>
       </c>
       <c r="E13" t="n">
-        <v>10212</v>
+        <v>5444</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9621</v>
+        <v>0.8176000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9991</v>
+        <v>0.9962000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9192</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,28 +841,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11442</v>
+        <v>11339</v>
       </c>
       <c r="D14" t="n">
-        <v>10921</v>
+        <v>9586</v>
       </c>
       <c r="E14" t="n">
-        <v>11395</v>
+        <v>9586</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9545</v>
+        <v>0.8454</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9959</v>
+        <v>0.8454</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9732</v>
+        <v>0.9806</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9645999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9512</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9549</v>
+        <v>0.9547</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9775</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9643999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.338</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7333</v>
+        <v>0.7045</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9872</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8895000000000001</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.9470000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9661</v>
+        <v>0.9656</v>
       </c>
     </row>
     <row r="11">
@@ -826,7 +826,7 @@
         <v>0.9962000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9262</v>
+        <v>0.9292</v>
       </c>
     </row>
     <row r="14">
@@ -856,7 +856,7 @@
         <v>0.8454</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9806</v>
+        <v>0.9768000000000001</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1867</v>
+        <v>1205</v>
       </c>
       <c r="D3" t="n">
-        <v>1520</v>
+        <v>417</v>
       </c>
       <c r="E3" t="n">
-        <v>1801</v>
+        <v>417</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8140999999999999</v>
+        <v>0.3461</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9645999999999999</v>
+        <v>0.3461</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.875</v>
+        <v>0.8853</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18642</v>
+        <v>15898</v>
       </c>
       <c r="D4" t="n">
-        <v>12073</v>
+        <v>2970</v>
       </c>
       <c r="E4" t="n">
-        <v>17732</v>
+        <v>2970</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6476000000000001</v>
+        <v>0.1868</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9512</v>
+        <v>0.1868</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9547</v>
+        <v>0.9359000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33173</v>
+        <v>27910</v>
       </c>
       <c r="D6" t="n">
-        <v>22126</v>
+        <v>10735</v>
       </c>
       <c r="E6" t="n">
-        <v>32425</v>
+        <v>10735</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.667</v>
+        <v>0.3846</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9775</v>
+        <v>0.3846</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9643999999999999</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5045</v>
+        <v>3691</v>
       </c>
       <c r="D7" t="n">
-        <v>1699</v>
+        <v>253</v>
       </c>
       <c r="E7" t="n">
-        <v>1705</v>
+        <v>253</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3368</v>
+        <v>0.06849999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.338</v>
+        <v>0.06849999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7045</v>
+        <v>0.6829000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7717</v>
+        <v>6077</v>
       </c>
       <c r="D8" t="n">
-        <v>5463</v>
+        <v>1058</v>
       </c>
       <c r="E8" t="n">
-        <v>7618</v>
+        <v>1058</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7079000000000001</v>
+        <v>0.1741</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9872</v>
+        <v>0.1741</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.883</v>
+        <v>0.8824</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4339</v>
+        <v>3726</v>
       </c>
       <c r="D10" t="n">
-        <v>3318</v>
+        <v>485</v>
       </c>
       <c r="E10" t="n">
-        <v>4109</v>
+        <v>485</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7646999999999999</v>
+        <v>0.1302</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9470000000000001</v>
+        <v>0.1302</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9656</v>
+        <v>0.9656999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5465</v>
+        <v>4949</v>
       </c>
       <c r="D13" t="n">
-        <v>4468</v>
+        <v>368</v>
       </c>
       <c r="E13" t="n">
-        <v>5444</v>
+        <v>368</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.8176000000000001</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9962000000000001</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9292</v>
+        <v>0.9143000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,28 +841,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11339</v>
+        <v>8117</v>
       </c>
       <c r="D14" t="n">
-        <v>9586</v>
+        <v>1764</v>
       </c>
       <c r="E14" t="n">
-        <v>9586</v>
+        <v>1764</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8454</v>
+        <v>0.2173</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.8454</v>
+        <v>0.2173</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9768000000000001</v>
+        <v>0.9823999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.3461</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8853</v>
+        <v>0.8904000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.1868</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9359000000000001</v>
+        <v>0.9370999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.3846</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9567</v>
+        <v>0.9568000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -686,7 +686,7 @@
         <v>0.1741</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8824</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.1302</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9656999999999999</v>
+        <v>0.9684</v>
       </c>
     </row>
     <row r="11">
@@ -826,7 +826,7 @@
         <v>0.07440000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9143000000000001</v>
+        <v>0.9187000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -856,7 +856,7 @@
         <v>0.2173</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.9826999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.3461</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8904000000000001</v>
+        <v>0.8884000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.1868</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9370999999999999</v>
+        <v>0.9351</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.3846</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9568000000000001</v>
+        <v>0.9555</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.06849999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6829000000000001</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.1741</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8903</v>
+        <v>0.8937999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -742,7 +742,7 @@
         <v>0.1302</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9684</v>
+        <v>0.9804999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -826,7 +826,7 @@
         <v>0.07440000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9187000000000001</v>
+        <v>0.9201</v>
       </c>
     </row>
     <row r="14">
@@ -856,7 +856,7 @@
         <v>0.2173</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9826999999999999</v>
+        <v>0.9843999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1205</v>
+        <v>1149</v>
       </c>
       <c r="D3" t="n">
-        <v>417</v>
+        <v>971</v>
       </c>
       <c r="E3" t="n">
-        <v>417</v>
+        <v>974</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.3461</v>
+        <v>0.8451000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.3461</v>
+        <v>0.8477</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8884000000000001</v>
+        <v>0.6225000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15898</v>
+        <v>17369</v>
       </c>
       <c r="D4" t="n">
-        <v>2970</v>
+        <v>10358</v>
       </c>
       <c r="E4" t="n">
-        <v>2970</v>
+        <v>17121</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1868</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1868</v>
+        <v>0.9856999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9351</v>
+        <v>0.6835</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27910</v>
+        <v>32359</v>
       </c>
       <c r="D6" t="n">
-        <v>10735</v>
+        <v>23979</v>
       </c>
       <c r="E6" t="n">
-        <v>10735</v>
+        <v>27082</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.3846</v>
+        <v>0.741</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3846</v>
+        <v>0.8369</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9555</v>
+        <v>0.8184</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3691</v>
+        <v>2212</v>
       </c>
       <c r="D7" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E7" t="n">
-        <v>253</v>
+        <v>2206</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.9973000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6923</v>
+        <v>0.5115999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6077</v>
+        <v>7337</v>
       </c>
       <c r="D8" t="n">
-        <v>1058</v>
+        <v>4867</v>
       </c>
       <c r="E8" t="n">
-        <v>1058</v>
+        <v>7035</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1741</v>
+        <v>0.6634</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1741</v>
+        <v>0.9588</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8937999999999999</v>
+        <v>0.7662</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,16 +701,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -718,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3726</v>
+        <v>4053</v>
       </c>
       <c r="D10" t="n">
-        <v>485</v>
+        <v>3012</v>
       </c>
       <c r="E10" t="n">
-        <v>485</v>
+        <v>3963</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.1302</v>
+        <v>0.7432</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.1302</v>
+        <v>0.9778</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.9804999999999999</v>
+        <v>0.5866</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E11" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -772,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -802,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4949</v>
+        <v>6238</v>
       </c>
       <c r="D13" t="n">
-        <v>368</v>
+        <v>5754</v>
       </c>
       <c r="E13" t="n">
-        <v>368</v>
+        <v>6238</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.07440000000000001</v>
+        <v>0.9224</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.07440000000000001</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.9201</v>
+        <v>0.5992000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8117</v>
+        <v>10330</v>
       </c>
       <c r="D14" t="n">
-        <v>1764</v>
+        <v>8519</v>
       </c>
       <c r="E14" t="n">
-        <v>1764</v>
+        <v>10253</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.2173</v>
+        <v>0.8247</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2173</v>
+        <v>0.9925</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9843999999999999</v>
+        <v>0.6662</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.8477</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6098</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9856999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6835</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.8369</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8184</v>
+        <v>0.8118000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9973000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5115999999999999</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9588</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7662</v>
+        <v>0.7595000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -746,7 +746,7 @@
         <v>0.9778</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.5866</v>
+        <v>0.5946</v>
       </c>
     </row>
     <row r="11">
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.475</v>
+        <v>0.4146</v>
       </c>
     </row>
     <row r="12">
@@ -830,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.5992000000000001</v>
+        <v>0.6163000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +860,7 @@
         <v>0.9925</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6662</v>
+        <v>0.6728000000000001</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1149</v>
+        <v>3017</v>
       </c>
       <c r="D3" t="n">
-        <v>971</v>
+        <v>2986</v>
       </c>
       <c r="E3" t="n">
-        <v>974</v>
+        <v>2999</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8451000000000001</v>
+        <v>0.9897</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.8477</v>
+        <v>0.9940000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6098</v>
+        <v>0.8009000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17369</v>
+        <v>22526</v>
       </c>
       <c r="D4" t="n">
-        <v>10358</v>
+        <v>21501</v>
       </c>
       <c r="E4" t="n">
-        <v>17121</v>
+        <v>22023</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.9545</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9856999999999999</v>
+        <v>0.9777</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.8368000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32359</v>
+        <v>38670</v>
       </c>
       <c r="D6" t="n">
-        <v>23979</v>
+        <v>30732</v>
       </c>
       <c r="E6" t="n">
-        <v>27082</v>
+        <v>32725</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.741</v>
+        <v>0.7947</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.8369</v>
+        <v>0.8462999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8118000000000001</v>
+        <v>0.8559</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2212</v>
+        <v>4794</v>
       </c>
       <c r="D7" t="n">
-        <v>250</v>
+        <v>2538</v>
       </c>
       <c r="E7" t="n">
-        <v>2206</v>
+        <v>4784</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.113</v>
+        <v>0.5294</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9973000000000001</v>
+        <v>0.9979</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.475</v>
+        <v>0.6744</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7337</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="n">
-        <v>4867</v>
+        <v>6812</v>
       </c>
       <c r="E8" t="n">
-        <v>7035</v>
+        <v>8353</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6634</v>
+        <v>0.8057</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9588</v>
+        <v>0.9879000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7595000000000001</v>
+        <v>0.8112999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4053</v>
+        <v>6198</v>
       </c>
       <c r="D10" t="n">
-        <v>3012</v>
+        <v>5795</v>
       </c>
       <c r="E10" t="n">
-        <v>3963</v>
+        <v>6043</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7432</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9778</v>
+        <v>0.975</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.5946</v>
+        <v>0.8222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="E11" t="n">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.4146</v>
+        <v>0.8889</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6238</v>
+        <v>9208</v>
       </c>
       <c r="D13" t="n">
-        <v>5754</v>
+        <v>9078</v>
       </c>
       <c r="E13" t="n">
-        <v>6238</v>
+        <v>9197</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9224</v>
+        <v>0.9859</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6163000000000001</v>
+        <v>0.7935</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10330</v>
+        <v>14474</v>
       </c>
       <c r="D14" t="n">
-        <v>8519</v>
+        <v>12983</v>
       </c>
       <c r="E14" t="n">
-        <v>10253</v>
+        <v>14318</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8247</v>
+        <v>0.897</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9925</v>
+        <v>0.9892</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6728000000000001</v>
+        <v>0.8641</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -885,7 +885,9 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H15"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3017</v>
+        <v>2671</v>
       </c>
       <c r="D3" t="n">
-        <v>2986</v>
+        <v>2573</v>
       </c>
       <c r="E3" t="n">
-        <v>2999</v>
+        <v>2573</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9897</v>
+        <v>0.9632999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9940000000000001</v>
+        <v>0.9632999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8009000000000001</v>
+        <v>0.6715000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22526</v>
+        <v>17009</v>
       </c>
       <c r="D4" t="n">
-        <v>21501</v>
+        <v>16403</v>
       </c>
       <c r="E4" t="n">
-        <v>22023</v>
+        <v>16763</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9545</v>
+        <v>0.9643999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9777</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8368000000000001</v>
+        <v>0.6815000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38670</v>
+        <v>36845</v>
       </c>
       <c r="D6" t="n">
-        <v>30732</v>
+        <v>31331</v>
       </c>
       <c r="E6" t="n">
-        <v>32725</v>
+        <v>36404</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7947</v>
+        <v>0.8503000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.8462999999999999</v>
+        <v>0.988</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8559</v>
+        <v>0.7863</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4794</v>
+        <v>3519</v>
       </c>
       <c r="D7" t="n">
-        <v>2538</v>
+        <v>3049</v>
       </c>
       <c r="E7" t="n">
-        <v>4784</v>
+        <v>3478</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5294</v>
+        <v>0.8664000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9979</v>
+        <v>0.9883</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6744</v>
+        <v>0.5965</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8455</v>
+        <v>7118</v>
       </c>
       <c r="D8" t="n">
-        <v>6812</v>
+        <v>6152</v>
       </c>
       <c r="E8" t="n">
-        <v>8353</v>
+        <v>6989</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8057</v>
+        <v>0.8643000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9879000000000001</v>
+        <v>0.9819</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8112999999999999</v>
+        <v>0.7222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,20 +701,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -722,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6198</v>
+        <v>4951</v>
       </c>
       <c r="D10" t="n">
-        <v>5795</v>
+        <v>4713</v>
       </c>
       <c r="E10" t="n">
-        <v>6043</v>
+        <v>4781</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9519</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.975</v>
+        <v>0.9656999999999999</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8222</v>
+        <v>0.7055</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +757,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E11" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,13 +772,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.8889</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +802,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +811,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9208</v>
+        <v>5771</v>
       </c>
       <c r="D13" t="n">
-        <v>9078</v>
+        <v>5671</v>
       </c>
       <c r="E13" t="n">
-        <v>9197</v>
+        <v>5760</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9859</v>
+        <v>0.9826999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9981</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.7935</v>
+        <v>0.6765000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +841,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14474</v>
+        <v>12573</v>
       </c>
       <c r="D14" t="n">
-        <v>12983</v>
+        <v>11195</v>
       </c>
       <c r="E14" t="n">
-        <v>14318</v>
+        <v>12335</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.897</v>
+        <v>0.8904000000000001</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9892</v>
+        <v>0.9811</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8641</v>
+        <v>0.6979000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2671</v>
+        <v>2127</v>
       </c>
       <c r="D3" t="n">
-        <v>2573</v>
+        <v>2061</v>
       </c>
       <c r="E3" t="n">
-        <v>2573</v>
+        <v>2061</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9632999999999999</v>
+        <v>0.9690000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9632999999999999</v>
+        <v>0.9690000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17009</v>
+        <v>18540</v>
       </c>
       <c r="D4" t="n">
-        <v>16403</v>
+        <v>18155</v>
       </c>
       <c r="E4" t="n">
-        <v>16763</v>
+        <v>18407</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9643999999999999</v>
+        <v>0.9792000000000001</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9854999999999999</v>
+        <v>0.9928</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6815000000000001</v>
+        <v>0.6302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36845</v>
+        <v>31626</v>
       </c>
       <c r="D6" t="n">
-        <v>31331</v>
+        <v>27282</v>
       </c>
       <c r="E6" t="n">
-        <v>36404</v>
+        <v>31616</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8503000000000001</v>
+        <v>0.8626</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.988</v>
+        <v>0.9997</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7863</v>
+        <v>0.7861</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3519</v>
+        <v>2925</v>
       </c>
       <c r="D7" t="n">
-        <v>3049</v>
+        <v>2829</v>
       </c>
       <c r="E7" t="n">
-        <v>3478</v>
+        <v>2908</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8664000000000001</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9883</v>
+        <v>0.9942</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5965</v>
+        <v>0.5385</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7118</v>
+        <v>6647</v>
       </c>
       <c r="D8" t="n">
-        <v>6152</v>
+        <v>5827</v>
       </c>
       <c r="E8" t="n">
-        <v>6989</v>
+        <v>6543</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8643000000000001</v>
+        <v>0.8765999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9819</v>
+        <v>0.9843999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7222</v>
+        <v>0.7556</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,16 +701,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -718,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4951</v>
+        <v>4590</v>
       </c>
       <c r="D10" t="n">
-        <v>4713</v>
+        <v>4335</v>
       </c>
       <c r="E10" t="n">
-        <v>4781</v>
+        <v>4384</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9519</v>
+        <v>0.9444</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9656999999999999</v>
+        <v>0.9551000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.7055</v>
+        <v>0.7005</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="E11" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -772,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.5333</v>
+        <v>0.5472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -802,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5771</v>
+        <v>5919</v>
       </c>
       <c r="D13" t="n">
-        <v>5671</v>
+        <v>5797</v>
       </c>
       <c r="E13" t="n">
-        <v>5760</v>
+        <v>5915</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9826999999999999</v>
+        <v>0.9793999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9981</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6765000000000001</v>
+        <v>0.5954999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12573</v>
+        <v>13055</v>
       </c>
       <c r="D14" t="n">
-        <v>11195</v>
+        <v>12083</v>
       </c>
       <c r="E14" t="n">
-        <v>12335</v>
+        <v>12715</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8904000000000001</v>
+        <v>0.9255</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9811</v>
+        <v>0.9740000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6979000000000001</v>
+        <v>0.6798000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2127</v>
+        <v>2313</v>
       </c>
       <c r="D3" t="n">
-        <v>2061</v>
+        <v>2275</v>
       </c>
       <c r="E3" t="n">
-        <v>2061</v>
+        <v>2300</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9690000000000001</v>
+        <v>0.9836</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9690000000000001</v>
+        <v>0.9944</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.626</v>
+        <v>0.6846</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18540</v>
+        <v>16788</v>
       </c>
       <c r="D4" t="n">
-        <v>18155</v>
+        <v>16521</v>
       </c>
       <c r="E4" t="n">
-        <v>18407</v>
+        <v>16774</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9792000000000001</v>
+        <v>0.9841</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9928</v>
+        <v>0.9992</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6302</v>
+        <v>0.6765000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31626</v>
+        <v>36232</v>
       </c>
       <c r="D6" t="n">
-        <v>27282</v>
+        <v>31259</v>
       </c>
       <c r="E6" t="n">
-        <v>31616</v>
+        <v>34877</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8626</v>
+        <v>0.8626999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9997</v>
+        <v>0.9626</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7861</v>
+        <v>0.8129000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2925</v>
+        <v>3034</v>
       </c>
       <c r="D7" t="n">
-        <v>2829</v>
+        <v>3031</v>
       </c>
       <c r="E7" t="n">
-        <v>2908</v>
+        <v>3032</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9942</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5385</v>
+        <v>0.6977</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6647</v>
+        <v>6957</v>
       </c>
       <c r="D8" t="n">
-        <v>5827</v>
+        <v>5987</v>
       </c>
       <c r="E8" t="n">
-        <v>6543</v>
+        <v>6867</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8765999999999999</v>
+        <v>0.8606</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9843999999999999</v>
+        <v>0.9871</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7556</v>
+        <v>0.7241</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4590</v>
+        <v>5922</v>
       </c>
       <c r="D10" t="n">
-        <v>4335</v>
+        <v>4377</v>
       </c>
       <c r="E10" t="n">
-        <v>4384</v>
+        <v>5456</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9444</v>
+        <v>0.7391</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9551000000000001</v>
+        <v>0.9213</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.7005</v>
+        <v>0.6737000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>269</v>
       </c>
       <c r="D11" t="n">
-        <v>119</v>
+        <v>269</v>
       </c>
       <c r="E11" t="n">
-        <v>119</v>
+        <v>269</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.5472</v>
+        <v>0.5702</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5919</v>
+        <v>7225</v>
       </c>
       <c r="D13" t="n">
-        <v>5797</v>
+        <v>7147</v>
       </c>
       <c r="E13" t="n">
-        <v>5915</v>
+        <v>7223</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9793999999999999</v>
+        <v>0.9892</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.5954999999999999</v>
+        <v>0.6051</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13055</v>
+        <v>14299</v>
       </c>
       <c r="D14" t="n">
-        <v>12083</v>
+        <v>13559</v>
       </c>
       <c r="E14" t="n">
-        <v>12715</v>
+        <v>14192</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9255</v>
+        <v>0.9481999999999999</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9740000000000001</v>
+        <v>0.9925</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6798000000000001</v>
+        <v>0.7087</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2313</v>
+        <v>2258</v>
       </c>
       <c r="D3" t="n">
-        <v>2275</v>
+        <v>1889</v>
       </c>
       <c r="E3" t="n">
-        <v>2300</v>
+        <v>2169</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9836</v>
+        <v>0.8366</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9944</v>
+        <v>0.9606</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6846</v>
+        <v>0.6408</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16788</v>
+        <v>15700</v>
       </c>
       <c r="D4" t="n">
-        <v>16521</v>
+        <v>12687</v>
       </c>
       <c r="E4" t="n">
-        <v>16774</v>
+        <v>14783</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9841</v>
+        <v>0.8081</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9992</v>
+        <v>0.9416</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6765000000000001</v>
+        <v>0.6195000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36232</v>
+        <v>29673</v>
       </c>
       <c r="D6" t="n">
-        <v>31259</v>
+        <v>23648</v>
       </c>
       <c r="E6" t="n">
-        <v>34877</v>
+        <v>27695</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8626999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9626</v>
+        <v>0.9333</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8129000000000001</v>
+        <v>0.7494</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3034</v>
+        <v>3245</v>
       </c>
       <c r="D7" t="n">
-        <v>3031</v>
+        <v>2358</v>
       </c>
       <c r="E7" t="n">
-        <v>3032</v>
+        <v>3245</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.7267</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9993000000000001</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6977</v>
+        <v>0.5957</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6957</v>
+        <v>5401</v>
       </c>
       <c r="D8" t="n">
-        <v>5987</v>
+        <v>4076</v>
       </c>
       <c r="E8" t="n">
-        <v>6867</v>
+        <v>4076</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8606</v>
+        <v>0.7547</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9871</v>
+        <v>0.7547</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7241</v>
+        <v>0.6531999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5922</v>
+        <v>4516</v>
       </c>
       <c r="D10" t="n">
-        <v>4377</v>
+        <v>3363</v>
       </c>
       <c r="E10" t="n">
-        <v>5456</v>
+        <v>3817</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7391</v>
+        <v>0.7447</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9213</v>
+        <v>0.8452</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6737000000000001</v>
+        <v>0.6008</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.5702</v>
+        <v>0.4087</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7225</v>
+        <v>4904</v>
       </c>
       <c r="D13" t="n">
-        <v>7147</v>
+        <v>4099</v>
       </c>
       <c r="E13" t="n">
-        <v>7223</v>
+        <v>4808</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9892</v>
+        <v>0.8358</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9997</v>
+        <v>0.9804</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6051</v>
+        <v>0.5846</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14299</v>
+        <v>13943</v>
       </c>
       <c r="D14" t="n">
-        <v>13559</v>
+        <v>11691</v>
       </c>
       <c r="E14" t="n">
-        <v>14192</v>
+        <v>11691</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9481999999999999</v>
+        <v>0.8384999999999999</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9925</v>
+        <v>0.8384999999999999</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.7087</v>
+        <v>0.6227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -885,9 +885,7 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H15" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H15"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2258</v>
+        <v>1754</v>
       </c>
       <c r="D3" t="n">
-        <v>1889</v>
+        <v>465</v>
       </c>
       <c r="E3" t="n">
-        <v>2169</v>
+        <v>465</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8366</v>
+        <v>0.2651</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9606</v>
+        <v>0.2651</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15700</v>
+        <v>13648</v>
       </c>
       <c r="D4" t="n">
-        <v>12687</v>
+        <v>2332</v>
       </c>
       <c r="E4" t="n">
-        <v>14783</v>
+        <v>2332</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8081</v>
+        <v>0.1709</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9416</v>
+        <v>0.1709</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29673</v>
+        <v>29578</v>
       </c>
       <c r="D6" t="n">
-        <v>23648</v>
+        <v>16120</v>
       </c>
       <c r="E6" t="n">
-        <v>27695</v>
+        <v>16120</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.797</v>
+        <v>0.545</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9333</v>
+        <v>0.545</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7494</v>
+        <v>0.1491</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3245</v>
+        <v>3037</v>
       </c>
       <c r="D7" t="n">
-        <v>2358</v>
+        <v>533</v>
       </c>
       <c r="E7" t="n">
-        <v>3245</v>
+        <v>533</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7267</v>
+        <v>0.1755</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>0.1755</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5957</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5401</v>
+        <v>5055</v>
       </c>
       <c r="D8" t="n">
-        <v>4076</v>
+        <v>875</v>
       </c>
       <c r="E8" t="n">
-        <v>4076</v>
+        <v>875</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7547</v>
+        <v>0.1731</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7547</v>
+        <v>0.1731</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6531999999999999</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,20 +701,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -722,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +727,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4516</v>
+        <v>3613</v>
       </c>
       <c r="D10" t="n">
-        <v>3363</v>
+        <v>445</v>
       </c>
       <c r="E10" t="n">
-        <v>3817</v>
+        <v>445</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7447</v>
+        <v>0.1232</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8452</v>
+        <v>0.1232</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6008</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +757,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,13 +772,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.4087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +802,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +811,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4904</v>
+        <v>2315</v>
       </c>
       <c r="D13" t="n">
-        <v>4099</v>
+        <v>505</v>
       </c>
       <c r="E13" t="n">
-        <v>4808</v>
+        <v>505</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.8358</v>
+        <v>0.2181</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9804</v>
+        <v>0.2181</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.5846</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +841,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13943</v>
+        <v>11667</v>
       </c>
       <c r="D14" t="n">
-        <v>11691</v>
+        <v>3388</v>
       </c>
       <c r="E14" t="n">
-        <v>11691</v>
+        <v>3388</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8384999999999999</v>
+        <v>0.2904</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.8384999999999999</v>
+        <v>0.2904</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6227</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1754</v>
+        <v>1839</v>
       </c>
       <c r="D3" t="n">
-        <v>465</v>
+        <v>1722</v>
       </c>
       <c r="E3" t="n">
-        <v>465</v>
+        <v>1724</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2651</v>
+        <v>0.9364</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2651</v>
+        <v>0.9375</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13648</v>
+        <v>18310</v>
       </c>
       <c r="D4" t="n">
-        <v>2332</v>
+        <v>16436</v>
       </c>
       <c r="E4" t="n">
-        <v>2332</v>
+        <v>17527</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1709</v>
+        <v>0.8976999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1709</v>
+        <v>0.9571999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.0125</v>
+        <v>0.5895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29578</v>
+        <v>36834</v>
       </c>
       <c r="D6" t="n">
-        <v>16120</v>
+        <v>29640</v>
       </c>
       <c r="E6" t="n">
-        <v>16120</v>
+        <v>36192</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.545</v>
+        <v>0.8047</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.545</v>
+        <v>0.9826</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1491</v>
+        <v>0.8204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>1445</v>
       </c>
       <c r="E7" t="n">
-        <v>533</v>
+        <v>3036</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1755</v>
+        <v>0.476</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1755</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0476</v>
+        <v>0.4878</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5055</v>
+        <v>6095</v>
       </c>
       <c r="D8" t="n">
-        <v>875</v>
+        <v>4059</v>
       </c>
       <c r="E8" t="n">
-        <v>875</v>
+        <v>5961</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1731</v>
+        <v>0.6659999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1731</v>
+        <v>0.978</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1</v>
+        <v>0.7531</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,16 +701,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -718,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -727,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3613</v>
+        <v>3410</v>
       </c>
       <c r="D10" t="n">
-        <v>445</v>
+        <v>2445</v>
       </c>
       <c r="E10" t="n">
-        <v>445</v>
+        <v>3172</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.1232</v>
+        <v>0.7170000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.1232</v>
+        <v>0.9301999999999999</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.0024</v>
+        <v>0.5760999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -772,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>0.4242</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -802,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2315</v>
+        <v>2556</v>
       </c>
       <c r="D13" t="n">
-        <v>505</v>
+        <v>2073</v>
       </c>
       <c r="E13" t="n">
-        <v>505</v>
+        <v>2460</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.2181</v>
+        <v>0.8109999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.2181</v>
+        <v>0.9623999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.01</v>
+        <v>0.5035000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11667</v>
+        <v>13288</v>
       </c>
       <c r="D14" t="n">
-        <v>3388</v>
+        <v>11168</v>
       </c>
       <c r="E14" t="n">
-        <v>3388</v>
+        <v>12662</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.2904</v>
+        <v>0.8405</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2904</v>
+        <v>0.9529000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.6856</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1839</v>
+        <v>3031</v>
       </c>
       <c r="D3" t="n">
-        <v>1722</v>
+        <v>2982</v>
       </c>
       <c r="E3" t="n">
-        <v>1724</v>
+        <v>2982</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9364</v>
+        <v>0.9838</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9375</v>
+        <v>0.9838</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6119</v>
+        <v>0.8367</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18310</v>
+        <v>21314</v>
       </c>
       <c r="D4" t="n">
-        <v>16436</v>
+        <v>19360</v>
       </c>
       <c r="E4" t="n">
-        <v>17527</v>
+        <v>19943</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8976999999999999</v>
+        <v>0.9083</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9571999999999999</v>
+        <v>0.9357</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.5895</v>
+        <v>0.8018000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36834</v>
+        <v>39740</v>
       </c>
       <c r="D6" t="n">
-        <v>29640</v>
+        <v>35040</v>
       </c>
       <c r="E6" t="n">
-        <v>36192</v>
+        <v>39570</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8047</v>
+        <v>0.8817</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9826</v>
+        <v>0.9956999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8204</v>
+        <v>0.8459</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3036</v>
+        <v>5179</v>
       </c>
       <c r="D7" t="n">
-        <v>1445</v>
+        <v>5079</v>
       </c>
       <c r="E7" t="n">
-        <v>3036</v>
+        <v>5171</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.476</v>
+        <v>0.9806999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>0.9984999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4878</v>
+        <v>0.8378</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6095</v>
+        <v>5934</v>
       </c>
       <c r="D8" t="n">
-        <v>4059</v>
+        <v>4203</v>
       </c>
       <c r="E8" t="n">
-        <v>5961</v>
+        <v>5918</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.7082999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.978</v>
+        <v>0.9973000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7531</v>
+        <v>0.6758</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +722,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3410</v>
+        <v>5497</v>
       </c>
       <c r="D10" t="n">
-        <v>2445</v>
+        <v>5302</v>
       </c>
       <c r="E10" t="n">
-        <v>3172</v>
+        <v>5359</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7170000000000001</v>
+        <v>0.9645</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9301999999999999</v>
+        <v>0.9749</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.8384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>339</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>339</v>
       </c>
       <c r="E11" t="n">
-        <v>165</v>
+        <v>339</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.4242</v>
+        <v>0.7903</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +815,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2556</v>
+        <v>11628</v>
       </c>
       <c r="D13" t="n">
-        <v>2073</v>
+        <v>11463</v>
       </c>
       <c r="E13" t="n">
-        <v>2460</v>
+        <v>11626</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.8109999999999999</v>
+        <v>0.9858</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9623999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.5035000000000001</v>
+        <v>0.8190000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +845,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13288</v>
+        <v>17765</v>
       </c>
       <c r="D14" t="n">
-        <v>11168</v>
+        <v>16423</v>
       </c>
       <c r="E14" t="n">
-        <v>12662</v>
+        <v>17539</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8405</v>
+        <v>0.9245</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9529000000000001</v>
+        <v>0.9873000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6856</v>
+        <v>0.8741</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -542,7 +542,7 @@
         <v>0.9838</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8367</v>
+        <v>0.8368000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v>0.9357</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8018000000000001</v>
+        <v>0.8072</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.9956999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8459</v>
+        <v>0.8481000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>0.9984999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8378</v>
+        <v>0.8286</v>
       </c>
     </row>
     <row r="8">
@@ -686,7 +686,7 @@
         <v>0.9973000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6758</v>
+        <v>0.6743000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -746,7 +746,7 @@
         <v>0.9749</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8384</v>
+        <v>0.8408</v>
       </c>
     </row>
     <row r="11">
@@ -830,7 +830,7 @@
         <v>0.9998</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.8112999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -860,7 +860,7 @@
         <v>0.9873000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8741</v>
+        <v>0.8691</v>
       </c>
     </row>
     <row r="15">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3031</v>
+        <v>2947</v>
       </c>
       <c r="D3" t="n">
-        <v>2982</v>
+        <v>2829</v>
       </c>
       <c r="E3" t="n">
-        <v>2982</v>
+        <v>2833</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9838</v>
+        <v>0.96</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9838</v>
+        <v>0.9612999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8368000000000001</v>
+        <v>0.6568000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21314</v>
+        <v>17996</v>
       </c>
       <c r="D4" t="n">
-        <v>19360</v>
+        <v>17195</v>
       </c>
       <c r="E4" t="n">
-        <v>19943</v>
+        <v>17364</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9083</v>
+        <v>0.9555</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9357</v>
+        <v>0.9649</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8072</v>
+        <v>0.6884999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,12 +597,14 @@
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,28 +613,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39740</v>
+        <v>37330</v>
       </c>
       <c r="D6" t="n">
-        <v>35040</v>
+        <v>32766</v>
       </c>
       <c r="E6" t="n">
-        <v>39570</v>
+        <v>37306</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8817</v>
+        <v>0.8776999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9956999999999999</v>
+        <v>0.9994</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8481000000000001</v>
+        <v>0.7720999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5179</v>
+        <v>4765</v>
       </c>
       <c r="D7" t="n">
-        <v>5079</v>
+        <v>4654</v>
       </c>
       <c r="E7" t="n">
-        <v>5171</v>
+        <v>4765</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9806999999999999</v>
+        <v>0.9767</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9984999999999999</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8286</v>
+        <v>0.7726999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,28 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5934</v>
+        <v>5194</v>
       </c>
       <c r="D8" t="n">
-        <v>4203</v>
+        <v>3850</v>
       </c>
       <c r="E8" t="n">
-        <v>5918</v>
+        <v>3850</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7082999999999999</v>
+        <v>0.7412000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9973000000000001</v>
+        <v>0.7412000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6743000000000001</v>
+        <v>0.6456999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,13 +703,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -722,7 +724,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,28 +733,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5497</v>
+        <v>4611</v>
       </c>
       <c r="D10" t="n">
-        <v>5302</v>
+        <v>4048</v>
       </c>
       <c r="E10" t="n">
-        <v>5359</v>
+        <v>4108</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9645</v>
+        <v>0.8779</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9749</v>
+        <v>0.8909</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8408</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,13 +763,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>339</v>
+        <v>203</v>
       </c>
       <c r="D11" t="n">
-        <v>339</v>
+        <v>203</v>
       </c>
       <c r="E11" t="n">
-        <v>339</v>
+        <v>203</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -776,13 +778,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.7903</v>
+        <v>0.4638</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -806,7 +808,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -815,28 +817,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11628</v>
+        <v>7113</v>
       </c>
       <c r="D13" t="n">
-        <v>11463</v>
+        <v>7001</v>
       </c>
       <c r="E13" t="n">
-        <v>11626</v>
+        <v>7097</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9858</v>
+        <v>0.9843000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9998</v>
+        <v>0.9978</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8112999999999999</v>
+        <v>0.6556999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,28 +847,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17765</v>
+        <v>15052</v>
       </c>
       <c r="D14" t="n">
-        <v>16423</v>
+        <v>13841</v>
       </c>
       <c r="E14" t="n">
-        <v>17539</v>
+        <v>14651</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9245</v>
+        <v>0.9195</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9873000000000001</v>
+        <v>0.9734</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8691</v>
+        <v>0.7001000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -885,7 +887,9 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H15"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2947</v>
+        <v>1996</v>
       </c>
       <c r="D3" t="n">
-        <v>2829</v>
+        <v>1972</v>
       </c>
       <c r="E3" t="n">
-        <v>2833</v>
+        <v>1973</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.96</v>
+        <v>0.988</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9612999999999999</v>
+        <v>0.9884999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6486</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17996</v>
+        <v>21098</v>
       </c>
       <c r="D4" t="n">
-        <v>17195</v>
+        <v>20613</v>
       </c>
       <c r="E4" t="n">
-        <v>17364</v>
+        <v>20713</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9555</v>
+        <v>0.977</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9649</v>
+        <v>0.9818000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6884999999999999</v>
+        <v>0.7907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,28 +613,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37330</v>
+        <v>31421</v>
       </c>
       <c r="D6" t="n">
-        <v>32766</v>
+        <v>27214</v>
       </c>
       <c r="E6" t="n">
-        <v>37306</v>
+        <v>31338</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8776999999999999</v>
+        <v>0.8661</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.9974</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7720999999999999</v>
+        <v>0.7186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4765</v>
+        <v>4381</v>
       </c>
       <c r="D7" t="n">
-        <v>4654</v>
+        <v>4376</v>
       </c>
       <c r="E7" t="n">
-        <v>4765</v>
+        <v>4379</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9989</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7726999999999999</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5194</v>
+        <v>5630</v>
       </c>
       <c r="D8" t="n">
-        <v>3850</v>
+        <v>4276</v>
       </c>
       <c r="E8" t="n">
-        <v>3850</v>
+        <v>5619</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7412000000000001</v>
+        <v>0.7595000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7412000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6456999999999999</v>
+        <v>0.7184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -724,7 +724,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -733,28 +733,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4611</v>
+        <v>3454</v>
       </c>
       <c r="D10" t="n">
-        <v>4048</v>
+        <v>3385</v>
       </c>
       <c r="E10" t="n">
-        <v>4108</v>
+        <v>3390</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8779</v>
+        <v>0.98</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8909</v>
+        <v>0.9815</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>423</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>423</v>
       </c>
       <c r="E11" t="n">
-        <v>203</v>
+        <v>423</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -778,13 +778,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.4638</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -808,7 +808,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -817,28 +817,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7113</v>
+        <v>5339</v>
       </c>
       <c r="D13" t="n">
-        <v>7001</v>
+        <v>5209</v>
       </c>
       <c r="E13" t="n">
-        <v>7097</v>
+        <v>5326</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9843000000000001</v>
+        <v>0.9756999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9978</v>
+        <v>0.9976</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.6509999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -847,28 +847,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15052</v>
+        <v>15644</v>
       </c>
       <c r="D14" t="n">
-        <v>13841</v>
+        <v>14134</v>
       </c>
       <c r="E14" t="n">
-        <v>14651</v>
+        <v>14134</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9195</v>
+        <v>0.9035</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9734</v>
+        <v>0.9035</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.7001000000000001</v>
+        <v>0.7212999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1996</v>
+        <v>1562</v>
       </c>
       <c r="D3" t="n">
-        <v>1972</v>
+        <v>766</v>
       </c>
       <c r="E3" t="n">
-        <v>1973</v>
+        <v>766</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.988</v>
+        <v>0.4904</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9884999999999999</v>
+        <v>0.4904</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21098</v>
+        <v>13049</v>
       </c>
       <c r="D4" t="n">
-        <v>20613</v>
+        <v>2084</v>
       </c>
       <c r="E4" t="n">
-        <v>20713</v>
+        <v>2084</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.977</v>
+        <v>0.1597</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9818000000000001</v>
+        <v>0.1597</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.7907</v>
+        <v>0.0131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,28 +613,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31421</v>
+        <v>27350</v>
       </c>
       <c r="D6" t="n">
-        <v>27214</v>
+        <v>15270</v>
       </c>
       <c r="E6" t="n">
-        <v>31338</v>
+        <v>15270</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8661</v>
+        <v>0.5583</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9974</v>
+        <v>0.5583</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7186</v>
+        <v>0.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4381</v>
+        <v>4956</v>
       </c>
       <c r="D7" t="n">
-        <v>4376</v>
+        <v>657</v>
       </c>
       <c r="E7" t="n">
-        <v>4379</v>
+        <v>657</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9989</v>
+        <v>0.1326</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.1326</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.0213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5630</v>
+        <v>4953</v>
       </c>
       <c r="D8" t="n">
-        <v>4276</v>
+        <v>647</v>
       </c>
       <c r="E8" t="n">
-        <v>5619</v>
+        <v>647</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7595000000000001</v>
+        <v>0.1306</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.998</v>
+        <v>0.1306</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7184</v>
+        <v>0.0629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,20 +703,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -724,7 +720,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -733,28 +729,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3454</v>
+        <v>2427</v>
       </c>
       <c r="D10" t="n">
-        <v>3385</v>
+        <v>392</v>
       </c>
       <c r="E10" t="n">
-        <v>3390</v>
+        <v>392</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.98</v>
+        <v>0.1615</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9815</v>
+        <v>0.1615</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6151</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -763,13 +759,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>423</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>423</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>423</v>
+        <v>21</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -778,13 +774,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.4375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -808,7 +804,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -817,28 +813,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5339</v>
+        <v>2415</v>
       </c>
       <c r="D13" t="n">
-        <v>5209</v>
+        <v>354</v>
       </c>
       <c r="E13" t="n">
-        <v>5326</v>
+        <v>354</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9756999999999999</v>
+        <v>0.1466</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9976</v>
+        <v>0.1466</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6509999999999999</v>
+        <v>0.0109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -847,28 +843,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15644</v>
+        <v>9794</v>
       </c>
       <c r="D14" t="n">
-        <v>14134</v>
+        <v>1509</v>
       </c>
       <c r="E14" t="n">
-        <v>14134</v>
+        <v>1509</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9035</v>
+        <v>0.1541</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9035</v>
+        <v>0.1541</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.7212999999999999</v>
+        <v>0.0183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1562</v>
+        <v>2041</v>
       </c>
       <c r="D3" t="n">
-        <v>766</v>
+        <v>1861</v>
       </c>
       <c r="E3" t="n">
-        <v>766</v>
+        <v>2040</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4904</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.4904</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>0.6256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13049</v>
+        <v>17937</v>
       </c>
       <c r="D4" t="n">
-        <v>2084</v>
+        <v>14938</v>
       </c>
       <c r="E4" t="n">
-        <v>2084</v>
+        <v>17413</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1597</v>
+        <v>0.8328</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1597</v>
+        <v>0.9708</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.6814</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,28 +613,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27350</v>
+        <v>33229</v>
       </c>
       <c r="D6" t="n">
-        <v>15270</v>
+        <v>27408</v>
       </c>
       <c r="E6" t="n">
-        <v>15270</v>
+        <v>33124</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.5583</v>
+        <v>0.8248000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5583</v>
+        <v>0.9968</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.0895</v>
+        <v>0.778</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4956</v>
+        <v>4341</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>580</v>
       </c>
       <c r="E7" t="n">
-        <v>657</v>
+        <v>3950</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1326</v>
+        <v>0.1336</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1326</v>
+        <v>0.9098999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0213</v>
+        <v>0.3617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4953</v>
+        <v>4973</v>
       </c>
       <c r="D8" t="n">
-        <v>647</v>
+        <v>3774</v>
       </c>
       <c r="E8" t="n">
-        <v>647</v>
+        <v>3774</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1306</v>
+        <v>0.7589</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1306</v>
+        <v>0.7589</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.0629</v>
+        <v>0.8534999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,28 +729,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2427</v>
+        <v>2859</v>
       </c>
       <c r="D10" t="n">
-        <v>392</v>
+        <v>2643</v>
       </c>
       <c r="E10" t="n">
-        <v>392</v>
+        <v>2715</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.1615</v>
+        <v>0.9244</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.1615</v>
+        <v>0.9495999999999999</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.5752</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -774,13 +774,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2415</v>
+        <v>1761</v>
       </c>
       <c r="D13" t="n">
-        <v>354</v>
+        <v>1518</v>
       </c>
       <c r="E13" t="n">
-        <v>354</v>
+        <v>1750</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.1466</v>
+        <v>0.862</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.1466</v>
+        <v>0.9937999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.0109</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -843,28 +843,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9794</v>
+        <v>12326</v>
       </c>
       <c r="D14" t="n">
-        <v>1509</v>
+        <v>10215</v>
       </c>
       <c r="E14" t="n">
-        <v>1509</v>
+        <v>12036</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.1541</v>
+        <v>0.8287</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.1541</v>
+        <v>0.9765</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.0183</v>
+        <v>0.6516</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -883,9 +883,7 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H15" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H15"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2041</v>
+        <v>3015</v>
       </c>
       <c r="D3" t="n">
-        <v>1861</v>
+        <v>2825</v>
       </c>
       <c r="E3" t="n">
-        <v>2040</v>
+        <v>3013</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6256</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17937</v>
+        <v>24563</v>
       </c>
       <c r="D4" t="n">
-        <v>14938</v>
+        <v>23091</v>
       </c>
       <c r="E4" t="n">
-        <v>17413</v>
+        <v>24279</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8328</v>
+        <v>0.9401</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9708</v>
+        <v>0.9884000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6814</v>
+        <v>0.8713</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,28 +613,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33229</v>
+        <v>37966</v>
       </c>
       <c r="D6" t="n">
-        <v>27408</v>
+        <v>33047</v>
       </c>
       <c r="E6" t="n">
-        <v>33124</v>
+        <v>37453</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8248000000000001</v>
+        <v>0.8704000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9968</v>
+        <v>0.9865</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.778</v>
+        <v>0.8162999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4341</v>
+        <v>7025</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>5926</v>
       </c>
       <c r="E7" t="n">
-        <v>3950</v>
+        <v>7009</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1336</v>
+        <v>0.8436</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9098999999999999</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3617</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4973</v>
+        <v>6031</v>
       </c>
       <c r="D8" t="n">
-        <v>3774</v>
+        <v>4663</v>
       </c>
       <c r="E8" t="n">
-        <v>3774</v>
+        <v>5972</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7589</v>
+        <v>0.7731999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7589</v>
+        <v>0.9902</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8534999999999999</v>
+        <v>0.7440000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,28 +729,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2859</v>
+        <v>5183</v>
       </c>
       <c r="D10" t="n">
-        <v>2643</v>
+        <v>4977</v>
       </c>
       <c r="E10" t="n">
-        <v>2715</v>
+        <v>5116</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9244</v>
+        <v>0.9603</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9495999999999999</v>
+        <v>0.9871</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.5752</v>
+        <v>0.8822</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -774,13 +774,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.4286</v>
+        <v>0.9037999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1761</v>
+        <v>8976</v>
       </c>
       <c r="D13" t="n">
-        <v>1518</v>
+        <v>8828</v>
       </c>
       <c r="E13" t="n">
-        <v>1750</v>
+        <v>8970</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.862</v>
+        <v>0.9834999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9937999999999999</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7944</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -843,28 +843,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12326</v>
+        <v>14821</v>
       </c>
       <c r="D14" t="n">
-        <v>10215</v>
+        <v>14262</v>
       </c>
       <c r="E14" t="n">
-        <v>12036</v>
+        <v>14649</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.8287</v>
+        <v>0.9623</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9765</v>
+        <v>0.9884000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6516</v>
+        <v>0.8656999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3015</v>
+        <v>2797</v>
       </c>
       <c r="D3" t="n">
-        <v>2825</v>
+        <v>2748</v>
       </c>
       <c r="E3" t="n">
-        <v>3013</v>
+        <v>2789</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9825</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9971</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8625</v>
+        <v>0.6518999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24563</v>
+        <v>24066</v>
       </c>
       <c r="D4" t="n">
-        <v>23091</v>
+        <v>23055</v>
       </c>
       <c r="E4" t="n">
-        <v>24279</v>
+        <v>23848</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9401</v>
+        <v>0.958</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9884000000000001</v>
+        <v>0.9909</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8713</v>
+        <v>0.7433</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,28 +613,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37966</v>
+        <v>38604</v>
       </c>
       <c r="D6" t="n">
-        <v>33047</v>
+        <v>34910</v>
       </c>
       <c r="E6" t="n">
-        <v>37453</v>
+        <v>38567</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8704000000000001</v>
+        <v>0.9043000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9865</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8162999999999999</v>
+        <v>0.7748</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7025</v>
+        <v>7555</v>
       </c>
       <c r="D7" t="n">
-        <v>5926</v>
+        <v>7062</v>
       </c>
       <c r="E7" t="n">
-        <v>7009</v>
+        <v>7297</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8436</v>
+        <v>0.9347</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.9659</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5814</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6031</v>
+        <v>6721</v>
       </c>
       <c r="D8" t="n">
-        <v>4663</v>
+        <v>5372</v>
       </c>
       <c r="E8" t="n">
-        <v>5972</v>
+        <v>6685</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7731999999999999</v>
+        <v>0.7993000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9902</v>
+        <v>0.9945999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7440000000000001</v>
+        <v>0.6609999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,28 +729,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5183</v>
+        <v>5779</v>
       </c>
       <c r="D10" t="n">
-        <v>4977</v>
+        <v>5570</v>
       </c>
       <c r="E10" t="n">
-        <v>5116</v>
+        <v>5726</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9603</v>
+        <v>0.9638</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9871</v>
+        <v>0.9908</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8822</v>
+        <v>0.6604000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>184</v>
+        <v>87</v>
       </c>
       <c r="E11" t="n">
-        <v>184</v>
+        <v>87</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -774,13 +774,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9037999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8976</v>
+        <v>5999</v>
       </c>
       <c r="D13" t="n">
-        <v>8828</v>
+        <v>5855</v>
       </c>
       <c r="E13" t="n">
-        <v>8970</v>
+        <v>5993</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9834999999999999</v>
+        <v>0.976</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.7944</v>
+        <v>0.6022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -843,28 +843,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14821</v>
+        <v>14860</v>
       </c>
       <c r="D14" t="n">
-        <v>14262</v>
+        <v>14180</v>
       </c>
       <c r="E14" t="n">
-        <v>14649</v>
+        <v>14750</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9623</v>
+        <v>0.9542</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9884000000000001</v>
+        <v>0.9926</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8656999999999999</v>
+        <v>0.6601</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2797</v>
+        <v>3207</v>
       </c>
       <c r="D3" t="n">
-        <v>2748</v>
+        <v>3166</v>
       </c>
       <c r="E3" t="n">
-        <v>2789</v>
+        <v>3166</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9825</v>
+        <v>0.9872</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9971</v>
+        <v>0.9872</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6518999999999999</v>
+        <v>0.7593000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24066</v>
+        <v>27962</v>
       </c>
       <c r="D4" t="n">
-        <v>23055</v>
+        <v>26773</v>
       </c>
       <c r="E4" t="n">
-        <v>23848</v>
+        <v>27556</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.958</v>
+        <v>0.9575</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9909</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.7433</v>
+        <v>0.7299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,28 +613,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38604</v>
+        <v>39307</v>
       </c>
       <c r="D6" t="n">
-        <v>34910</v>
+        <v>35027</v>
       </c>
       <c r="E6" t="n">
-        <v>38567</v>
+        <v>37827</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9043000000000001</v>
+        <v>0.8911</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9623</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7748</v>
+        <v>0.8027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7555</v>
+        <v>9038</v>
       </c>
       <c r="D7" t="n">
-        <v>7062</v>
+        <v>8430</v>
       </c>
       <c r="E7" t="n">
-        <v>7297</v>
+        <v>8788</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9347</v>
+        <v>0.9327</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9659</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.625</v>
+        <v>0.6829000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6721</v>
+        <v>6261</v>
       </c>
       <c r="D8" t="n">
-        <v>5372</v>
+        <v>5194</v>
       </c>
       <c r="E8" t="n">
-        <v>6685</v>
+        <v>6234</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7993000000000001</v>
+        <v>0.8295999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9945999999999999</v>
+        <v>0.9956999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6609999999999999</v>
+        <v>0.6446</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,28 +729,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5779</v>
+        <v>5688</v>
       </c>
       <c r="D10" t="n">
-        <v>5570</v>
+        <v>5504</v>
       </c>
       <c r="E10" t="n">
-        <v>5726</v>
+        <v>5557</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9638</v>
+        <v>0.9677</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9908</v>
+        <v>0.977</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6604000000000001</v>
+        <v>0.6881999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -774,13 +774,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6627</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5999</v>
+        <v>5235</v>
       </c>
       <c r="D13" t="n">
-        <v>5855</v>
+        <v>5066</v>
       </c>
       <c r="E13" t="n">
-        <v>5993</v>
+        <v>5234</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.976</v>
+        <v>0.9677</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6022</v>
+        <v>0.6353</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -843,28 +843,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14860</v>
+        <v>15085</v>
       </c>
       <c r="D14" t="n">
-        <v>14180</v>
+        <v>14020</v>
       </c>
       <c r="E14" t="n">
-        <v>14750</v>
+        <v>15021</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9542</v>
+        <v>0.9294</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9926</v>
+        <v>0.9958</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6601</v>
+        <v>0.7140000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -883,7 +883,9 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H15"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3207</v>
+        <v>3323</v>
       </c>
       <c r="D3" t="n">
-        <v>3166</v>
+        <v>2926</v>
       </c>
       <c r="E3" t="n">
-        <v>3166</v>
+        <v>3264</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9872</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9872</v>
+        <v>0.9822</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.7593000000000001</v>
+        <v>0.6414</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27962</v>
+        <v>22506</v>
       </c>
       <c r="D4" t="n">
-        <v>26773</v>
+        <v>15658</v>
       </c>
       <c r="E4" t="n">
-        <v>27556</v>
+        <v>20211</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9575</v>
+        <v>0.6957</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9854999999999999</v>
+        <v>0.898</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.7299</v>
+        <v>0.7040000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,28 +613,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39307</v>
+        <v>36758</v>
       </c>
       <c r="D6" t="n">
-        <v>35027</v>
+        <v>28742</v>
       </c>
       <c r="E6" t="n">
-        <v>37827</v>
+        <v>33729</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8911</v>
+        <v>0.7818999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9623</v>
+        <v>0.9176000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8027</v>
+        <v>0.8092</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9038</v>
+        <v>7893</v>
       </c>
       <c r="D7" t="n">
-        <v>8430</v>
+        <v>2574</v>
       </c>
       <c r="E7" t="n">
-        <v>8788</v>
+        <v>7171</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9327</v>
+        <v>0.3261</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9085</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6829000000000001</v>
+        <v>0.4878</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6261</v>
+        <v>6354</v>
       </c>
       <c r="D8" t="n">
-        <v>5194</v>
+        <v>4329</v>
       </c>
       <c r="E8" t="n">
-        <v>6234</v>
+        <v>4329</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8295999999999999</v>
+        <v>0.6812999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9956999999999999</v>
+        <v>0.6812999999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6446</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,16 +703,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
@@ -720,7 +724,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,28 +733,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5688</v>
+        <v>4945</v>
       </c>
       <c r="D10" t="n">
-        <v>5504</v>
+        <v>3695</v>
       </c>
       <c r="E10" t="n">
-        <v>5557</v>
+        <v>4592</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9677</v>
+        <v>0.7472</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.977</v>
+        <v>0.9286</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6881999999999999</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -759,13 +763,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="E11" t="n">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -774,13 +778,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.6627</v>
+        <v>0.5109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -804,7 +808,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -813,28 +817,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5235</v>
+        <v>6033</v>
       </c>
       <c r="D13" t="n">
-        <v>5066</v>
+        <v>4375</v>
       </c>
       <c r="E13" t="n">
-        <v>5234</v>
+        <v>5954</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9677</v>
+        <v>0.7252</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9998</v>
+        <v>0.9869</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6353</v>
+        <v>0.5975</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -843,28 +847,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15085</v>
+        <v>14303</v>
       </c>
       <c r="D14" t="n">
-        <v>14020</v>
+        <v>11575</v>
       </c>
       <c r="E14" t="n">
-        <v>15021</v>
+        <v>11575</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9294</v>
+        <v>0.8093</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.9958</v>
+        <v>0.8093</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.7140000000000001</v>
+        <v>0.6493000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Taxa de Coleta no Prazo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coleta no Prazo'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coleta no Prazo'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -494,405 +494,285 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CARAP 02-SP</t>
+          <t>CHM-SP</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>18691</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3139</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="2" t="n"/>
+        <v>3139</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.0131</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CARAP-SP</t>
+          <t>CLP-SP</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3323</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3264</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.8804999999999999</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.9822</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.6414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHM-SP</t>
+          <t>F JND-SP</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22506</v>
+        <v>9424</v>
       </c>
       <c r="D4" t="n">
-        <v>15658</v>
+        <v>580</v>
       </c>
       <c r="E4" t="n">
-        <v>20211</v>
+        <v>580</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6957</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.898</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.7040000000000001</v>
+        <v>0.06059999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CLP-SP</t>
+          <t>F S-JRG-SP</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>6444</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1106</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="3" t="n"/>
+        <v>1106</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.1716</v>
+      </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>0.1364</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COT-SP</t>
+          <t>ITUP-SP</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36758</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>28742</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>33729</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.7818999999999999</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.9176000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="2" t="n">
-        <v>0.8092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F JND-SP</t>
+          <t>JND 02-SP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7893</v>
+        <v>3484</v>
       </c>
       <c r="D7" t="n">
-        <v>2574</v>
+        <v>612</v>
       </c>
       <c r="E7" t="n">
-        <v>7171</v>
+        <v>612</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3261</v>
+        <v>0.1757</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9085</v>
+        <v>0.1757</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4878</v>
+        <v>0.0158</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F S-JRG-SP</t>
+          <t>JND-SP</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6354</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>4329</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>4329</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6812999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.6812999999999999</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.65</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ITUP-SP</t>
+          <t>OSC 02-SP</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JND 02-SP</t>
+          <t>OSC-SP</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4945</v>
+        <v>3343</v>
       </c>
       <c r="D10" t="n">
-        <v>3695</v>
+        <v>261</v>
       </c>
       <c r="E10" t="n">
-        <v>4592</v>
+        <v>261</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7472</v>
+        <v>0.0781</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9286</v>
+        <v>0.0781</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.636</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JND-SP</t>
+          <t>S-FREG-SP</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>216</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="2" t="n">
-        <v>0.5109</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>OSC 02-SP</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>OSC-SP</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>6033</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4375</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5954</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.7252</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0.9869</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0.5975</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>S-CSVD-SP</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>14303</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11575</v>
-      </c>
-      <c r="E14" t="n">
-        <v>11575</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.8093</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.8093</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0.6493000000000001</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S-FREG-SP</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Taxa de Coleta no Prazo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coleta no Prazo'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coleta no Prazo'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18691</v>
+        <v>20930</v>
       </c>
       <c r="D2" t="n">
-        <v>3139</v>
+        <v>15442</v>
       </c>
       <c r="E2" t="n">
-        <v>3139</v>
+        <v>19994</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1679</v>
+        <v>0.7378</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1679</v>
+        <v>0.9553</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.6962</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9424</v>
+        <v>5213</v>
       </c>
       <c r="D4" t="n">
-        <v>580</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>580</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.06150000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.06150000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.1852</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,28 +587,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6444</v>
+        <v>5932</v>
       </c>
       <c r="D5" t="n">
-        <v>1106</v>
+        <v>4327</v>
       </c>
       <c r="E5" t="n">
-        <v>1106</v>
+        <v>5871</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1716</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1716</v>
+        <v>0.9897</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1364</v>
+        <v>0.7681</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -617,16 +617,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
@@ -634,7 +638,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +647,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3484</v>
+        <v>5636</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>4865</v>
       </c>
       <c r="E7" t="n">
-        <v>612</v>
+        <v>5066</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1757</v>
+        <v>0.8632</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1757</v>
+        <v>0.8989</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.5815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,13 +677,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>248</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>248</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>248</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -688,91 +692,67 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.5753</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OSC 02-SP</t>
+          <t>S-CSVD-SP</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>11032</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="2" t="n"/>
+        <v>10840</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.8158</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.6352</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OSC-SP</t>
+          <t>S-FREG-SP</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3343</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>261</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.0781</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0.0781</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="3" t="n"/>
       <c r="H10" s="2" t="n">
-        <v>0.0033</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>S-FREG-SP</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20930</v>
+        <v>33767</v>
       </c>
       <c r="D2" t="n">
-        <v>15442</v>
+        <v>30110</v>
       </c>
       <c r="E2" t="n">
-        <v>19994</v>
+        <v>33566</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.7378</v>
+        <v>0.8917</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9553</v>
+        <v>0.9940000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.6962</v>
+        <v>0.8623999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,12 +543,14 @@
       </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="3" t="n"/>
-      <c r="H3" s="2" t="n"/>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,28 +559,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5213</v>
+        <v>1587</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>1423</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0025</v>
+        <v>0.0158</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.1852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,28 +589,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5932</v>
+        <v>7358</v>
       </c>
       <c r="D5" t="n">
-        <v>4327</v>
+        <v>4764</v>
       </c>
       <c r="E5" t="n">
-        <v>5871</v>
+        <v>7309</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7293999999999999</v>
+        <v>0.6475</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9897</v>
+        <v>0.9933</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.7681</v>
+        <v>0.6867</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,7 +640,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -647,28 +649,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5636</v>
+        <v>13436</v>
       </c>
       <c r="D7" t="n">
-        <v>4865</v>
+        <v>9355</v>
       </c>
       <c r="E7" t="n">
-        <v>5066</v>
+        <v>9452</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8632</v>
+        <v>0.6962999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8989</v>
+        <v>0.7034999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5815</v>
+        <v>0.8706999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -677,13 +679,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="E8" t="n">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -692,13 +694,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.5753</v>
+        <v>0.7237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -707,28 +709,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11032</v>
+        <v>16998</v>
       </c>
       <c r="D9" t="n">
-        <v>9000</v>
+        <v>15158</v>
       </c>
       <c r="E9" t="n">
-        <v>10840</v>
+        <v>16881</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8158</v>
+        <v>0.8918</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9826</v>
+        <v>0.9931</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6352</v>
+        <v>0.8637</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -747,9 +749,7 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H10" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33767</v>
+        <v>27434</v>
       </c>
       <c r="D2" t="n">
-        <v>30110</v>
+        <v>24827</v>
       </c>
       <c r="E2" t="n">
-        <v>33566</v>
+        <v>27230</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.8917</v>
+        <v>0.905</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9940000000000001</v>
+        <v>0.9926</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.8623999999999999</v>
+        <v>0.6983</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,28 +559,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1587</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1423</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.0158</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.8967000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -589,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7358</v>
+        <v>9336</v>
       </c>
       <c r="D5" t="n">
-        <v>4764</v>
+        <v>5909</v>
       </c>
       <c r="E5" t="n">
-        <v>7309</v>
+        <v>9299</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6475</v>
+        <v>0.6329</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9933</v>
+        <v>0.996</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6867</v>
+        <v>0.7006</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -619,13 +615,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -640,7 +636,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -649,28 +645,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13436</v>
+        <v>16921</v>
       </c>
       <c r="D7" t="n">
-        <v>9355</v>
+        <v>9663</v>
       </c>
       <c r="E7" t="n">
-        <v>9452</v>
+        <v>9962</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6962999999999999</v>
+        <v>0.5710999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.7034999999999999</v>
+        <v>0.5887</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8706999999999999</v>
+        <v>0.6783</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -679,13 +675,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>452</v>
       </c>
       <c r="D8" t="n">
-        <v>281</v>
+        <v>452</v>
       </c>
       <c r="E8" t="n">
-        <v>281</v>
+        <v>452</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -694,13 +690,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7237</v>
+        <v>0.5698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -709,28 +705,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16998</v>
+        <v>20427</v>
       </c>
       <c r="D9" t="n">
-        <v>15158</v>
+        <v>18467</v>
       </c>
       <c r="E9" t="n">
-        <v>16881</v>
+        <v>20264</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8918</v>
+        <v>0.904</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9931</v>
+        <v>0.992</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.8637</v>
+        <v>0.7376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -749,7 +745,9 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27434</v>
+        <v>28530</v>
       </c>
       <c r="D2" t="n">
-        <v>24827</v>
+        <v>26541</v>
       </c>
       <c r="E2" t="n">
-        <v>27230</v>
+        <v>28523</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.905</v>
+        <v>0.9303</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9926</v>
+        <v>0.9998</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.6983</v>
+        <v>0.7595000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -570,13 +570,13 @@
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="2" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9336</v>
+        <v>10397</v>
       </c>
       <c r="D5" t="n">
-        <v>5909</v>
+        <v>6463</v>
       </c>
       <c r="E5" t="n">
-        <v>9299</v>
+        <v>10362</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6329</v>
+        <v>0.6215999999999999</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.996</v>
+        <v>0.9965999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.7006</v>
+        <v>0.6968000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -645,28 +645,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16921</v>
+        <v>16076</v>
       </c>
       <c r="D7" t="n">
-        <v>9663</v>
+        <v>10159</v>
       </c>
       <c r="E7" t="n">
-        <v>9962</v>
+        <v>11246</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5710999999999999</v>
+        <v>0.6319</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5887</v>
+        <v>0.6995999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6783</v>
+        <v>0.7262999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>452</v>
+        <v>898</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>898</v>
       </c>
       <c r="E8" t="n">
-        <v>452</v>
+        <v>898</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -690,13 +690,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.5698</v>
+        <v>0.5205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -705,28 +705,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20427</v>
+        <v>17540</v>
       </c>
       <c r="D9" t="n">
-        <v>18467</v>
+        <v>15750</v>
       </c>
       <c r="E9" t="n">
-        <v>20264</v>
+        <v>17430</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.904</v>
+        <v>0.8979</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.992</v>
+        <v>0.9937</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.7376</v>
+        <v>0.7623000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28530</v>
+        <v>28292</v>
       </c>
       <c r="D2" t="n">
-        <v>26541</v>
+        <v>26580</v>
       </c>
       <c r="E2" t="n">
-        <v>28523</v>
+        <v>28255</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9303</v>
+        <v>0.9395</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9998</v>
+        <v>0.9987</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.7595000000000001</v>
+        <v>0.7386</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10397</v>
+        <v>8469</v>
       </c>
       <c r="D5" t="n">
-        <v>6463</v>
+        <v>5951</v>
       </c>
       <c r="E5" t="n">
-        <v>10362</v>
+        <v>8323</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6215999999999999</v>
+        <v>0.7027</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9828</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6968000000000001</v>
+        <v>0.657</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -615,20 +615,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
@@ -636,7 +632,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -645,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16076</v>
+        <v>14354</v>
       </c>
       <c r="D7" t="n">
-        <v>10159</v>
+        <v>12342</v>
       </c>
       <c r="E7" t="n">
-        <v>11246</v>
+        <v>12912</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6319</v>
+        <v>0.8598</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6995999999999999</v>
+        <v>0.8995000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.6774</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -675,13 +671,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>898</v>
+        <v>540</v>
       </c>
       <c r="D8" t="n">
-        <v>898</v>
+        <v>540</v>
       </c>
       <c r="E8" t="n">
-        <v>898</v>
+        <v>540</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -690,13 +686,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.5205</v>
+        <v>0.6119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -705,28 +701,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17540</v>
+        <v>14683</v>
       </c>
       <c r="D9" t="n">
-        <v>15750</v>
+        <v>12986</v>
       </c>
       <c r="E9" t="n">
-        <v>17430</v>
+        <v>14632</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8979</v>
+        <v>0.8844</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9937</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.7623000000000001</v>
+        <v>0.7462000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28292</v>
+        <v>25681</v>
       </c>
       <c r="D2" t="n">
-        <v>26580</v>
+        <v>16214</v>
       </c>
       <c r="E2" t="n">
-        <v>28255</v>
+        <v>17524</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9395</v>
+        <v>0.6314</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9987</v>
+        <v>0.6823999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.7386</v>
+        <v>0.6674</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8469</v>
+        <v>9279</v>
       </c>
       <c r="D5" t="n">
-        <v>5951</v>
+        <v>6926</v>
       </c>
       <c r="E5" t="n">
-        <v>8323</v>
+        <v>9068</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7027</v>
+        <v>0.7464</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9828</v>
+        <v>0.9773000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.657</v>
+        <v>0.5909</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14354</v>
+        <v>12184</v>
       </c>
       <c r="D7" t="n">
-        <v>12342</v>
+        <v>8846</v>
       </c>
       <c r="E7" t="n">
-        <v>12912</v>
+        <v>8960</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8598</v>
+        <v>0.726</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8995000000000001</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6774</v>
+        <v>0.6353</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,13 +671,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>540</v>
+        <v>165</v>
       </c>
       <c r="D8" t="n">
-        <v>540</v>
+        <v>165</v>
       </c>
       <c r="E8" t="n">
-        <v>540</v>
+        <v>165</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -686,13 +686,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6119</v>
+        <v>0.5781000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,28 +701,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14683</v>
+        <v>13062</v>
       </c>
       <c r="D9" t="n">
-        <v>12986</v>
+        <v>9988</v>
       </c>
       <c r="E9" t="n">
-        <v>14632</v>
+        <v>12943</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8844</v>
+        <v>0.7646999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9909</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.7462000000000001</v>
+        <v>0.6866</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -741,9 +741,7 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H10" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25681</v>
+        <v>22432</v>
       </c>
       <c r="D2" t="n">
-        <v>16214</v>
+        <v>3065</v>
       </c>
       <c r="E2" t="n">
-        <v>17524</v>
+        <v>3065</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.6314</v>
+        <v>0.1366</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.6823999999999999</v>
+        <v>0.1366</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.6674</v>
+        <v>0.0443</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9279</v>
+        <v>6352</v>
       </c>
       <c r="D5" t="n">
-        <v>6926</v>
+        <v>1249</v>
       </c>
       <c r="E5" t="n">
-        <v>9068</v>
+        <v>1249</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7464</v>
+        <v>0.1966</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9773000000000001</v>
+        <v>0.1966</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.5909</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -625,14 +625,12 @@
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +639,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12184</v>
+        <v>12146</v>
       </c>
       <c r="D7" t="n">
-        <v>8846</v>
+        <v>1847</v>
       </c>
       <c r="E7" t="n">
-        <v>8960</v>
+        <v>1847</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.726</v>
+        <v>0.1521</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.1521</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6353</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,13 +669,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -686,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.5781000000000001</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,28 +699,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13062</v>
+        <v>12317</v>
       </c>
       <c r="D9" t="n">
-        <v>9988</v>
+        <v>2551</v>
       </c>
       <c r="E9" t="n">
-        <v>12943</v>
+        <v>2551</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.7646999999999999</v>
+        <v>0.2071</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9909</v>
+        <v>0.2071</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6866</v>
+        <v>0.07820000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -741,7 +739,9 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22432</v>
+        <v>26829</v>
       </c>
       <c r="D2" t="n">
-        <v>3065</v>
+        <v>3899</v>
       </c>
       <c r="E2" t="n">
-        <v>3065</v>
+        <v>3899</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1366</v>
+        <v>0.1453</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1366</v>
+        <v>0.1453</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.0443</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6352</v>
+        <v>6131</v>
       </c>
       <c r="D5" t="n">
-        <v>1249</v>
+        <v>110</v>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>110</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1966</v>
+        <v>0.0179</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1966</v>
+        <v>0.0179</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.16</v>
+        <v>0.0305</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -639,28 +639,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12146</v>
+        <v>9365</v>
       </c>
       <c r="D7" t="n">
-        <v>1847</v>
+        <v>2313</v>
       </c>
       <c r="E7" t="n">
-        <v>1847</v>
+        <v>2313</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1521</v>
+        <v>0.247</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1521</v>
+        <v>0.247</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0367</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -669,28 +669,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="2" t="n">
-        <v>0.0392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -699,28 +695,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12317</v>
+        <v>11505</v>
       </c>
       <c r="D9" t="n">
-        <v>2551</v>
+        <v>1490</v>
       </c>
       <c r="E9" t="n">
-        <v>2551</v>
+        <v>1490</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.2071</v>
+        <v>0.1295</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.2071</v>
+        <v>0.1295</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -739,9 +735,7 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H10" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26829</v>
+        <v>30392</v>
       </c>
       <c r="D2" t="n">
-        <v>3899</v>
+        <v>20071</v>
       </c>
       <c r="E2" t="n">
-        <v>3899</v>
+        <v>30345</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1453</v>
+        <v>0.6604000000000001</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1453</v>
+        <v>0.9984999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.0596</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6131</v>
+        <v>7563</v>
       </c>
       <c r="D5" t="n">
-        <v>110</v>
+        <v>5319</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>7540</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.0179</v>
+        <v>0.7033</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.0179</v>
+        <v>0.997</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.0305</v>
+        <v>0.7963</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -625,12 +625,14 @@
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -639,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9365</v>
+        <v>12456</v>
       </c>
       <c r="D7" t="n">
-        <v>2313</v>
+        <v>8403</v>
       </c>
       <c r="E7" t="n">
-        <v>2313</v>
+        <v>8557</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.247</v>
+        <v>0.6746</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.247</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.8797</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -680,13 +682,13 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>0.9129999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -695,28 +697,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11505</v>
+        <v>15322</v>
       </c>
       <c r="D9" t="n">
-        <v>1490</v>
+        <v>9370</v>
       </c>
       <c r="E9" t="n">
-        <v>1490</v>
+        <v>15006</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.1295</v>
+        <v>0.6114999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.1295</v>
+        <v>0.9793999999999999</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.0168</v>
+        <v>0.9253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30392</v>
+        <v>31688</v>
       </c>
       <c r="D2" t="n">
-        <v>20071</v>
+        <v>25661</v>
       </c>
       <c r="E2" t="n">
-        <v>30345</v>
+        <v>31680</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.6604000000000001</v>
+        <v>0.8098000000000001</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9997</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.885</v>
+        <v>0.7181999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7563</v>
+        <v>6529</v>
       </c>
       <c r="D5" t="n">
-        <v>5319</v>
+        <v>4680</v>
       </c>
       <c r="E5" t="n">
-        <v>7540</v>
+        <v>4680</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7033</v>
+        <v>0.7168000000000001</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.997</v>
+        <v>0.7168000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.7963</v>
+        <v>0.6552</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12456</v>
+        <v>11792</v>
       </c>
       <c r="D7" t="n">
-        <v>8403</v>
+        <v>9230</v>
       </c>
       <c r="E7" t="n">
-        <v>8557</v>
+        <v>10288</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6746</v>
+        <v>0.7827</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8797</v>
+        <v>0.7645000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,24 +671,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="3" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H8" s="2" t="n">
-        <v>0.9129999999999999</v>
+        <v>0.6786</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -697,28 +701,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15322</v>
+        <v>20410</v>
       </c>
       <c r="D9" t="n">
-        <v>9370</v>
+        <v>18432</v>
       </c>
       <c r="E9" t="n">
-        <v>15006</v>
+        <v>20286</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.6114999999999999</v>
+        <v>0.9031</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9793999999999999</v>
+        <v>0.9939</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.9253</v>
+        <v>0.8567</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -737,7 +741,9 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31688</v>
+        <v>27969</v>
       </c>
       <c r="D2" t="n">
-        <v>25661</v>
+        <v>26083</v>
       </c>
       <c r="E2" t="n">
-        <v>31680</v>
+        <v>27964</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.8098000000000001</v>
+        <v>0.9326000000000001</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9997</v>
+        <v>0.9998</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.6794</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6529</v>
+        <v>5868</v>
       </c>
       <c r="D5" t="n">
         <v>4680</v>
       </c>
       <c r="E5" t="n">
-        <v>4680</v>
+        <v>5865</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7168000000000001</v>
+        <v>0.7975</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.7168000000000001</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6552</v>
+        <v>0.6196</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11792</v>
+        <v>13041</v>
       </c>
       <c r="D7" t="n">
-        <v>9230</v>
+        <v>12312</v>
       </c>
       <c r="E7" t="n">
-        <v>10288</v>
+        <v>12801</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7827</v>
+        <v>0.9440999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.9815999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7645000000000001</v>
+        <v>0.6758</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,13 +671,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -686,13 +686,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6786</v>
+        <v>0.5263</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,28 +701,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20410</v>
+        <v>13536</v>
       </c>
       <c r="D9" t="n">
-        <v>18432</v>
+        <v>11785</v>
       </c>
       <c r="E9" t="n">
-        <v>20286</v>
+        <v>13498</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9031</v>
+        <v>0.8706</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9939</v>
+        <v>0.9972</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.8567</v>
+        <v>0.7292000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -741,9 +741,7 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H10" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27969</v>
+        <v>25292</v>
       </c>
       <c r="D2" t="n">
-        <v>26083</v>
+        <v>24359</v>
       </c>
       <c r="E2" t="n">
-        <v>27964</v>
+        <v>25259</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9326000000000001</v>
+        <v>0.9631000000000001</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9998</v>
+        <v>0.9987</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.6794</v>
+        <v>0.6829999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5868</v>
+        <v>5943</v>
       </c>
       <c r="D5" t="n">
-        <v>4680</v>
+        <v>4959</v>
       </c>
       <c r="E5" t="n">
-        <v>5865</v>
+        <v>5942</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7975</v>
+        <v>0.8344</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6196</v>
+        <v>0.6108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13041</v>
+        <v>13975</v>
       </c>
       <c r="D7" t="n">
-        <v>12312</v>
+        <v>12690</v>
       </c>
       <c r="E7" t="n">
-        <v>12801</v>
+        <v>13436</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9440999999999999</v>
+        <v>0.9081</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9815999999999999</v>
+        <v>0.9614</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6758</v>
+        <v>0.6357</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,13 +671,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -686,13 +686,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.5263</v>
+        <v>0.6296</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,28 +701,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13536</v>
+        <v>13277</v>
       </c>
       <c r="D9" t="n">
-        <v>11785</v>
+        <v>12618</v>
       </c>
       <c r="E9" t="n">
-        <v>13498</v>
+        <v>13262</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8706</v>
+        <v>0.9504</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9972</v>
+        <v>0.9989</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.7292000000000001</v>
+        <v>0.6943</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25292</v>
+        <v>22512</v>
       </c>
       <c r="D2" t="n">
-        <v>24359</v>
+        <v>16603</v>
       </c>
       <c r="E2" t="n">
-        <v>25259</v>
+        <v>21901</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9631000000000001</v>
+        <v>0.7375</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9987</v>
+        <v>0.9729000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.6829999999999999</v>
+        <v>0.6987000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,14 +543,12 @@
       </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="3" t="n"/>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5943</v>
+        <v>5461</v>
       </c>
       <c r="D5" t="n">
-        <v>4959</v>
+        <v>4098</v>
       </c>
       <c r="E5" t="n">
-        <v>5942</v>
+        <v>5456</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8344</v>
+        <v>0.7504000000000001</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9998</v>
+        <v>0.9991</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6108</v>
+        <v>0.6581999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -632,7 +630,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -641,28 +639,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13975</v>
+        <v>13290</v>
       </c>
       <c r="D7" t="n">
-        <v>12690</v>
+        <v>7290</v>
       </c>
       <c r="E7" t="n">
-        <v>13436</v>
+        <v>10112</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9081</v>
+        <v>0.5485</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9614</v>
+        <v>0.7609</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6357</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,13 +669,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -686,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6296</v>
+        <v>0.7143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -701,28 +699,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13277</v>
+        <v>11970</v>
       </c>
       <c r="D9" t="n">
-        <v>12618</v>
+        <v>9502</v>
       </c>
       <c r="E9" t="n">
-        <v>13262</v>
+        <v>11829</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9504</v>
+        <v>0.7938</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9989</v>
+        <v>0.9882</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6943</v>
+        <v>0.6221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -741,7 +739,9 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22512</v>
+        <v>18480</v>
       </c>
       <c r="D2" t="n">
-        <v>16603</v>
+        <v>3125</v>
       </c>
       <c r="E2" t="n">
-        <v>21901</v>
+        <v>3125</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.7375</v>
+        <v>0.1691</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9729000000000001</v>
+        <v>0.1691</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.6987000000000001</v>
+        <v>0.0692</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5461</v>
+        <v>5001</v>
       </c>
       <c r="D5" t="n">
-        <v>4098</v>
+        <v>716</v>
       </c>
       <c r="E5" t="n">
-        <v>5456</v>
+        <v>716</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7504000000000001</v>
+        <v>0.1432</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9991</v>
+        <v>0.1432</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6581999999999999</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -639,28 +639,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13290</v>
+        <v>10192</v>
       </c>
       <c r="D7" t="n">
-        <v>7290</v>
+        <v>1472</v>
       </c>
       <c r="E7" t="n">
-        <v>10112</v>
+        <v>1472</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5485</v>
+        <v>0.1444</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.7609</v>
+        <v>0.1444</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.512</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7143</v>
+        <v>0.0323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -699,28 +699,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11970</v>
+        <v>10448</v>
       </c>
       <c r="D9" t="n">
-        <v>9502</v>
+        <v>2289</v>
       </c>
       <c r="E9" t="n">
-        <v>11829</v>
+        <v>2289</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.7938</v>
+        <v>0.2191</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9882</v>
+        <v>0.2191</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6221</v>
+        <v>0.04559999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18480</v>
+        <v>26447</v>
       </c>
       <c r="D2" t="n">
-        <v>3125</v>
+        <v>20123</v>
       </c>
       <c r="E2" t="n">
-        <v>3125</v>
+        <v>26253</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1691</v>
+        <v>0.7609</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1691</v>
+        <v>0.9926999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.0692</v>
+        <v>0.7126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5001</v>
+        <v>6419</v>
       </c>
       <c r="D5" t="n">
-        <v>716</v>
+        <v>4866</v>
       </c>
       <c r="E5" t="n">
-        <v>716</v>
+        <v>6415</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1432</v>
+        <v>0.7581</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1432</v>
+        <v>0.9994</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.12</v>
+        <v>0.6857</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,16 +613,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
@@ -630,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -639,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10192</v>
+        <v>9779</v>
       </c>
       <c r="D7" t="n">
-        <v>1472</v>
+        <v>4701</v>
       </c>
       <c r="E7" t="n">
-        <v>1472</v>
+        <v>5673</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1444</v>
+        <v>0.4807</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1444</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0243</v>
+        <v>0.4675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -669,28 +673,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="2" t="n">
-        <v>0.0323</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -699,28 +699,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10448</v>
+        <v>12616</v>
       </c>
       <c r="D9" t="n">
-        <v>2289</v>
+        <v>8990</v>
       </c>
       <c r="E9" t="n">
-        <v>2289</v>
+        <v>12553</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.2191</v>
+        <v>0.7126</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.2191</v>
+        <v>0.995</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.5943999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -739,9 +739,7 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="H10" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26447</v>
+        <v>25996</v>
       </c>
       <c r="D2" t="n">
-        <v>20123</v>
+        <v>23372</v>
       </c>
       <c r="E2" t="n">
-        <v>26253</v>
+        <v>25983</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.7609</v>
+        <v>0.8991</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9926999999999999</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.7126</v>
+        <v>0.7198</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6419</v>
+        <v>6305</v>
       </c>
       <c r="D5" t="n">
-        <v>4866</v>
+        <v>5119</v>
       </c>
       <c r="E5" t="n">
-        <v>6415</v>
+        <v>6301</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7581</v>
+        <v>0.8119</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0.9994</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6857</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -634,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9779</v>
+        <v>13324</v>
       </c>
       <c r="D7" t="n">
-        <v>4701</v>
+        <v>10366</v>
       </c>
       <c r="E7" t="n">
-        <v>5673</v>
+        <v>10729</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4807</v>
+        <v>0.778</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.8051999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4675</v>
+        <v>0.8370000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,24 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H8" s="2" t="n">
-        <v>0.48</v>
+        <v>0.8056</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -699,28 +703,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12616</v>
+        <v>17588</v>
       </c>
       <c r="D9" t="n">
-        <v>8990</v>
+        <v>13803</v>
       </c>
       <c r="E9" t="n">
-        <v>12553</v>
+        <v>17500</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.7126</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0.995</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.5943999999999999</v>
+        <v>0.8276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25996</v>
+        <v>22645</v>
       </c>
       <c r="D2" t="n">
-        <v>23372</v>
+        <v>21886</v>
       </c>
       <c r="E2" t="n">
-        <v>25983</v>
+        <v>22644</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.8991</v>
+        <v>0.9665</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.7198</v>
+        <v>0.7287</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6305</v>
+        <v>5714</v>
       </c>
       <c r="D5" t="n">
-        <v>5119</v>
+        <v>4690</v>
       </c>
       <c r="E5" t="n">
-        <v>6301</v>
+        <v>5711</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8119</v>
+        <v>0.8208</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9994</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.8244</v>
+        <v>0.6815000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -634,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13324</v>
+        <v>11330</v>
       </c>
       <c r="D7" t="n">
-        <v>10366</v>
+        <v>10044</v>
       </c>
       <c r="E7" t="n">
-        <v>10729</v>
+        <v>10387</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.778</v>
+        <v>0.8865000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8051999999999999</v>
+        <v>0.9168000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8370000000000001</v>
+        <v>0.7167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -688,13 +688,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8056</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,28 +703,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17588</v>
+        <v>15981</v>
       </c>
       <c r="D9" t="n">
-        <v>13803</v>
+        <v>13319</v>
       </c>
       <c r="E9" t="n">
-        <v>17500</v>
+        <v>15926</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.8334</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.995</v>
+        <v>0.9965999999999999</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.8276</v>
+        <v>0.7081000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22645</v>
+        <v>27165</v>
       </c>
       <c r="D2" t="n">
-        <v>21886</v>
+        <v>26974</v>
       </c>
       <c r="E2" t="n">
-        <v>22644</v>
+        <v>27164</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9665</v>
+        <v>0.993</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.7287</v>
+        <v>0.8164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5714</v>
+        <v>5925</v>
       </c>
       <c r="D5" t="n">
-        <v>4690</v>
+        <v>4365</v>
       </c>
       <c r="E5" t="n">
-        <v>5711</v>
+        <v>5902</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8208</v>
+        <v>0.7367</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9961</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6815000000000001</v>
+        <v>0.657</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -634,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11330</v>
+        <v>12260</v>
       </c>
       <c r="D7" t="n">
-        <v>10044</v>
+        <v>11880</v>
       </c>
       <c r="E7" t="n">
-        <v>10387</v>
+        <v>12185</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8865000000000001</v>
+        <v>0.9690000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9168000000000001</v>
+        <v>0.9939</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7167</v>
+        <v>0.6955</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -688,13 +688,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,28 +703,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15981</v>
+        <v>15597</v>
       </c>
       <c r="D9" t="n">
-        <v>13319</v>
+        <v>13816</v>
       </c>
       <c r="E9" t="n">
-        <v>15926</v>
+        <v>15403</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8334</v>
+        <v>0.8858</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9876</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.7081000000000001</v>
+        <v>0.6939</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27165</v>
+        <v>23062</v>
       </c>
       <c r="D2" t="n">
-        <v>26974</v>
+        <v>21992</v>
       </c>
       <c r="E2" t="n">
-        <v>27164</v>
+        <v>22807</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.993</v>
+        <v>0.9536</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>0.9889</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.8164</v>
+        <v>0.5543</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5925</v>
+        <v>7134</v>
       </c>
       <c r="D5" t="n">
-        <v>4365</v>
+        <v>5411</v>
       </c>
       <c r="E5" t="n">
-        <v>5902</v>
+        <v>7032</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7367</v>
+        <v>0.7585</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9961</v>
+        <v>0.9856999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.657</v>
+        <v>0.6312</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -634,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12260</v>
+        <v>12235</v>
       </c>
       <c r="D7" t="n">
-        <v>11880</v>
+        <v>11754</v>
       </c>
       <c r="E7" t="n">
-        <v>12185</v>
+        <v>12232</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9690000000000001</v>
+        <v>0.9606999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9939</v>
+        <v>0.9998</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6955</v>
+        <v>0.6888</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -688,13 +688,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6222</v>
+        <v>0.5366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,28 +703,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15597</v>
+        <v>13419</v>
       </c>
       <c r="D9" t="n">
-        <v>13816</v>
+        <v>12374</v>
       </c>
       <c r="E9" t="n">
-        <v>15403</v>
+        <v>13337</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8858</v>
+        <v>0.9220999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9876</v>
+        <v>0.9939</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6939</v>
+        <v>0.6881</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23062</v>
+        <v>20084</v>
       </c>
       <c r="D2" t="n">
-        <v>21992</v>
+        <v>14321</v>
       </c>
       <c r="E2" t="n">
-        <v>22807</v>
+        <v>20046</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9536</v>
+        <v>0.7131000000000001</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9889</v>
+        <v>0.9981</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.5543</v>
+        <v>0.4042</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7134</v>
+        <v>6195</v>
       </c>
       <c r="D5" t="n">
-        <v>5411</v>
+        <v>4018</v>
       </c>
       <c r="E5" t="n">
-        <v>7032</v>
+        <v>6143</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7585</v>
+        <v>0.6486</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9856999999999999</v>
+        <v>0.9915999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6312</v>
+        <v>0.6867</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -634,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12235</v>
+        <v>10085</v>
       </c>
       <c r="D7" t="n">
-        <v>11754</v>
+        <v>5479</v>
       </c>
       <c r="E7" t="n">
-        <v>12232</v>
+        <v>8097</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9606999999999999</v>
+        <v>0.5433</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9998</v>
+        <v>0.8029000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6888</v>
+        <v>0.6657</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -688,13 +688,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.5366</v>
+        <v>0.4884000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,28 +703,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13419</v>
+        <v>11690</v>
       </c>
       <c r="D9" t="n">
-        <v>12374</v>
+        <v>9317</v>
       </c>
       <c r="E9" t="n">
-        <v>13337</v>
+        <v>11280</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9220999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9939</v>
+        <v>0.9649</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6881</v>
+        <v>0.6243</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20084</v>
+        <v>15368</v>
       </c>
       <c r="D2" t="n">
-        <v>14321</v>
+        <v>2636</v>
       </c>
       <c r="E2" t="n">
-        <v>20046</v>
+        <v>2636</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.7131000000000001</v>
+        <v>0.1715</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9981</v>
+        <v>0.1715</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.4042</v>
+        <v>0.07519999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6195</v>
+        <v>5630</v>
       </c>
       <c r="D5" t="n">
-        <v>4018</v>
+        <v>951</v>
       </c>
       <c r="E5" t="n">
-        <v>6143</v>
+        <v>951</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6486</v>
+        <v>0.1689</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9915999999999999</v>
+        <v>0.1689</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6867</v>
+        <v>0.0699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,20 +613,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
@@ -634,7 +630,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +639,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10085</v>
+        <v>8222</v>
       </c>
       <c r="D7" t="n">
-        <v>5479</v>
+        <v>1246</v>
       </c>
       <c r="E7" t="n">
-        <v>8097</v>
+        <v>1246</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5433</v>
+        <v>0.1515</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8029000000000001</v>
+        <v>0.1515</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6657</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,13 +669,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -688,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4884000000000001</v>
+        <v>0.03700000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,28 +699,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11690</v>
+        <v>9978</v>
       </c>
       <c r="D9" t="n">
-        <v>9317</v>
+        <v>2078</v>
       </c>
       <c r="E9" t="n">
-        <v>11280</v>
+        <v>2078</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.797</v>
+        <v>0.2083</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9649</v>
+        <v>0.2083</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6243</v>
+        <v>0.0257</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15368</v>
+        <v>16188</v>
       </c>
       <c r="D2" t="n">
-        <v>2636</v>
+        <v>13819</v>
       </c>
       <c r="E2" t="n">
-        <v>2636</v>
+        <v>14580</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1715</v>
+        <v>0.8537</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1715</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.07519999999999999</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5630</v>
+        <v>4538</v>
       </c>
       <c r="D5" t="n">
-        <v>951</v>
+        <v>3053</v>
       </c>
       <c r="E5" t="n">
-        <v>951</v>
+        <v>4514</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1689</v>
+        <v>0.6728000000000001</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1689</v>
+        <v>0.9947</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.0699</v>
+        <v>0.6405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,16 +613,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
@@ -630,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -639,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8222</v>
+        <v>7195</v>
       </c>
       <c r="D7" t="n">
-        <v>1246</v>
+        <v>4220</v>
       </c>
       <c r="E7" t="n">
-        <v>1246</v>
+        <v>5193</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1515</v>
+        <v>0.5865</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1515</v>
+        <v>0.7218000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0297</v>
+        <v>0.5367000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -669,13 +673,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -684,13 +688,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.5556</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -699,28 +703,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9978</v>
+        <v>9164</v>
       </c>
       <c r="D9" t="n">
-        <v>2078</v>
+        <v>6906</v>
       </c>
       <c r="E9" t="n">
-        <v>2078</v>
+        <v>8190</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.2083</v>
+        <v>0.7536</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.2083</v>
+        <v>0.8937</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.0257</v>
+        <v>0.5284</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16188</v>
+        <v>22963</v>
       </c>
       <c r="D2" t="n">
-        <v>13819</v>
+        <v>22066</v>
       </c>
       <c r="E2" t="n">
-        <v>14580</v>
+        <v>22085</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.8537</v>
+        <v>0.9609000000000001</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9618000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.74</v>
+        <v>0.8645999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4538</v>
+        <v>4854</v>
       </c>
       <c r="D5" t="n">
-        <v>3053</v>
+        <v>3870</v>
       </c>
       <c r="E5" t="n">
-        <v>4514</v>
+        <v>4851</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6728000000000001</v>
+        <v>0.7973</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9947</v>
+        <v>0.9994</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6405</v>
+        <v>0.7006</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,20 +613,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
@@ -634,7 +630,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +639,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7195</v>
+        <v>12653</v>
       </c>
       <c r="D7" t="n">
-        <v>4220</v>
+        <v>10979</v>
       </c>
       <c r="E7" t="n">
-        <v>5193</v>
+        <v>12642</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5865</v>
+        <v>0.8676999999999999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.7218000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5367000000000001</v>
+        <v>0.8765000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,13 +669,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -688,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.5556</v>
+        <v>0.7273000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,28 +699,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9164</v>
+        <v>13072</v>
       </c>
       <c r="D9" t="n">
-        <v>6906</v>
+        <v>11888</v>
       </c>
       <c r="E9" t="n">
-        <v>8190</v>
+        <v>12921</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.7536</v>
+        <v>0.9094</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8937</v>
+        <v>0.9884000000000001</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.5284</v>
+        <v>0.8358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22963</v>
+        <v>23655</v>
       </c>
       <c r="D2" t="n">
-        <v>22066</v>
+        <v>22557</v>
       </c>
       <c r="E2" t="n">
-        <v>22085</v>
+        <v>23655</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9609000000000001</v>
+        <v>0.9536</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9618000000000001</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.8645999999999999</v>
+        <v>0.7454000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4854</v>
+        <v>4464</v>
       </c>
       <c r="D5" t="n">
-        <v>3870</v>
+        <v>4150</v>
       </c>
       <c r="E5" t="n">
-        <v>4851</v>
+        <v>4464</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7973</v>
+        <v>0.9297</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.7006</v>
+        <v>0.6851999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,16 +613,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="3" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
@@ -630,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -639,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12653</v>
+        <v>12972</v>
       </c>
       <c r="D7" t="n">
-        <v>10979</v>
+        <v>12069</v>
       </c>
       <c r="E7" t="n">
-        <v>12642</v>
+        <v>12971</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8676999999999999</v>
+        <v>0.9304000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8765000000000001</v>
+        <v>0.7276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -669,13 +673,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -684,13 +688,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7273000000000001</v>
+        <v>0.4571</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -699,28 +703,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13072</v>
+        <v>10556</v>
       </c>
       <c r="D9" t="n">
-        <v>11888</v>
+        <v>10162</v>
       </c>
       <c r="E9" t="n">
-        <v>12921</v>
+        <v>10474</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9094</v>
+        <v>0.9627</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9884000000000001</v>
+        <v>0.9922</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.8358</v>
+        <v>0.6755</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23655</v>
+        <v>21563</v>
       </c>
       <c r="D2" t="n">
-        <v>22557</v>
+        <v>20363</v>
       </c>
       <c r="E2" t="n">
-        <v>23655</v>
+        <v>21556</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9536</v>
+        <v>0.9443</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.7454000000000001</v>
+        <v>0.7169</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,22 +533,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +578,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,28 +587,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4464</v>
+        <v>4912</v>
       </c>
       <c r="D5" t="n">
-        <v>4150</v>
+        <v>4231</v>
       </c>
       <c r="E5" t="n">
-        <v>4464</v>
+        <v>4912</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9297</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6851999999999999</v>
+        <v>0.6271</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -634,7 +638,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,28 +647,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12972</v>
+        <v>13674</v>
       </c>
       <c r="D7" t="n">
-        <v>12069</v>
+        <v>13002</v>
       </c>
       <c r="E7" t="n">
-        <v>12971</v>
+        <v>13668</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9304000000000001</v>
+        <v>0.9509000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7276</v>
+        <v>0.6823</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,28 +677,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="2" t="n">
-        <v>0.4571</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,28 +703,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10556</v>
+        <v>9781</v>
       </c>
       <c r="D9" t="n">
-        <v>10162</v>
+        <v>9419</v>
       </c>
       <c r="E9" t="n">
-        <v>10474</v>
+        <v>9711</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9627</v>
+        <v>0.963</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9922</v>
+        <v>0.9928</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6755</v>
+        <v>0.6603</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/PICKUP_diario.xlsx
+++ b/output/PICKUP_diario.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21563</v>
+        <v>21377</v>
       </c>
       <c r="D2" t="n">
-        <v>20363</v>
+        <v>20612</v>
       </c>
       <c r="E2" t="n">
-        <v>21556</v>
+        <v>21352</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9443</v>
+        <v>0.9642000000000001</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9997</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.7169</v>
+        <v>0.7776000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,26 +533,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -578,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,28 +583,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4912</v>
+        <v>5112</v>
       </c>
       <c r="D5" t="n">
-        <v>4231</v>
+        <v>4534</v>
       </c>
       <c r="E5" t="n">
-        <v>4912</v>
+        <v>5112</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8869</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6271</v>
+        <v>0.6529</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -647,28 +643,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13674</v>
+        <v>14633</v>
       </c>
       <c r="D7" t="n">
-        <v>13002</v>
+        <v>14186</v>
       </c>
       <c r="E7" t="n">
-        <v>13668</v>
+        <v>14633</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9509000000000001</v>
+        <v>0.9695</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9995999999999999</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6823</v>
+        <v>0.7171999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -677,24 +673,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="3" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H8" s="2" t="n">
-        <v>0.4286</v>
+        <v>0.6429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -703,28 +703,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9781</v>
+        <v>10346</v>
       </c>
       <c r="D9" t="n">
-        <v>9419</v>
+        <v>9933</v>
       </c>
       <c r="E9" t="n">
-        <v>9711</v>
+        <v>10309</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.963</v>
+        <v>0.9601000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9928</v>
+        <v>0.9964</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6603</v>
+        <v>0.6951999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
